--- a/utils/data-room-simulator/output/trial_balance.xlsx
+++ b/utils/data-room-simulator/output/trial_balance.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trial Balance" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Trial Balance" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,161 +413,161 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE62"/>
+  <dimension ref="A1:AE63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>period</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>year</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>month</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>acct_4000</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>acct_4100</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>acct_4200</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>acct_5000</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>acct_5100</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>acct_5200</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>acct_6000</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>acct_6100</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>acct_6200</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>acct_1000</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>acct_1100</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>acct_prepaid</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>acct_fixed_assets</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>acct_accum_depr</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>acct_2000</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>acct_accrued</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>acct_deferred</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>acct_2500</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>acct_3000</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>acct_3200</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="X1" t="inlineStr">
         <is>
           <t>total_revenue</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="Y1" t="inlineStr">
         <is>
           <t>total_cogs</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>gross_profit</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>total_opex</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AB1" t="inlineStr">
         <is>
           <t>net_income</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>total_assets</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>total_liabilities</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>total_equity</t>
         </is>
@@ -598,88 +586,88 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>-2431168.51</v>
+        <v>-1380726.26</v>
       </c>
       <c r="E2" t="n">
-        <v>-286019.82</v>
+        <v>-162438.38</v>
       </c>
       <c r="F2" t="n">
-        <v>-143009.91</v>
+        <v>-81219.19</v>
       </c>
       <c r="G2" t="n">
-        <v>297460.62</v>
+        <v>212794.28</v>
       </c>
       <c r="H2" t="n">
-        <v>223095.46</v>
+        <v>159595.71</v>
       </c>
       <c r="I2" t="n">
-        <v>74365.14999999999</v>
+        <v>53198.57</v>
       </c>
       <c r="J2" t="n">
-        <v>715049.5600000001</v>
+        <v>406095.96</v>
       </c>
       <c r="K2" t="n">
-        <v>572039.65</v>
+        <v>324876.77</v>
       </c>
       <c r="L2" t="n">
-        <v>429029.74</v>
+        <v>243657.58</v>
       </c>
       <c r="M2" t="n">
-        <v>57203.96</v>
+        <v>32487.68</v>
       </c>
       <c r="N2" t="n">
-        <v>4179999.49</v>
+        <v>2563729.71</v>
       </c>
       <c r="O2" t="n">
-        <v>57203.96</v>
+        <v>32487.68</v>
       </c>
       <c r="P2" t="n">
-        <v>6167977.33</v>
+        <v>3392931.71</v>
       </c>
       <c r="Q2" t="n">
-        <v>-30334.31</v>
+        <v>-16417.41</v>
       </c>
       <c r="R2" t="n">
-        <v>-967799.36</v>
+        <v>-744547.1800000001</v>
       </c>
       <c r="S2" t="n">
-        <v>-85805.95</v>
+        <v>-48731.52</v>
       </c>
       <c r="T2" t="n">
-        <v>-2412902.93</v>
+        <v>-2234626.15</v>
       </c>
       <c r="U2" t="n">
-        <v>-4360391.69</v>
+        <v>-1622172.31</v>
       </c>
       <c r="V2" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W2" t="n">
-        <v>-549158.0600000001</v>
+        <v>-224164.97</v>
       </c>
       <c r="X2" t="n">
-        <v>2860198.25</v>
+        <v>1624383.84</v>
       </c>
       <c r="Y2" t="n">
-        <v>594921.24</v>
+        <v>425588.57</v>
       </c>
       <c r="Z2" t="n">
-        <v>2265277.01</v>
+        <v>1198795.27</v>
       </c>
       <c r="AA2" t="n">
-        <v>1716118.95</v>
+        <v>974630.3</v>
       </c>
       <c r="AB2" t="n">
-        <v>549158.0600000001</v>
+        <v>224164.97</v>
       </c>
       <c r="AC2" t="n">
-        <v>10432050.44</v>
+        <v>6005219.37</v>
       </c>
       <c r="AD2" t="n">
-        <v>7826899.93</v>
+        <v>4650077.16</v>
       </c>
       <c r="AE2" t="n">
-        <v>2605150.51</v>
+        <v>1355142.21</v>
       </c>
     </row>
     <row r="3">
@@ -695,88 +683,88 @@
         <v>2</v>
       </c>
       <c r="D3" t="n">
-        <v>-2621695.63</v>
+        <v>-1376521.35</v>
       </c>
       <c r="E3" t="n">
-        <v>-308434.78</v>
+        <v>-161943.69</v>
       </c>
       <c r="F3" t="n">
-        <v>-154217.39</v>
+        <v>-80971.84</v>
       </c>
       <c r="G3" t="n">
-        <v>320772.17</v>
+        <v>212146.23</v>
       </c>
       <c r="H3" t="n">
-        <v>240579.13</v>
+        <v>159109.67</v>
       </c>
       <c r="I3" t="n">
-        <v>80193.03999999999</v>
+        <v>53036.56</v>
       </c>
       <c r="J3" t="n">
-        <v>771086.95</v>
+        <v>404859.22</v>
       </c>
       <c r="K3" t="n">
-        <v>616869.5600000001</v>
+        <v>323887.38</v>
       </c>
       <c r="L3" t="n">
-        <v>462652.17</v>
+        <v>242915.53</v>
       </c>
       <c r="M3" t="n">
-        <v>61686.96</v>
+        <v>32388.74</v>
       </c>
       <c r="N3" t="n">
-        <v>4911728.21</v>
+        <v>2282617.17</v>
       </c>
       <c r="O3" t="n">
-        <v>61686.96</v>
+        <v>32388.74</v>
       </c>
       <c r="P3" t="n">
-        <v>6180313.29</v>
+        <v>3399717.58</v>
       </c>
       <c r="Q3" t="n">
-        <v>-60789.97</v>
+        <v>-32900.49</v>
       </c>
       <c r="R3" t="n">
-        <v>-1327300.07</v>
+        <v>-799618.03</v>
       </c>
       <c r="S3" t="n">
-        <v>-92530.42999999999</v>
+        <v>-48583.11</v>
       </c>
       <c r="T3" t="n">
-        <v>-3162311.15</v>
+        <v>-2167428.67</v>
       </c>
       <c r="U3" t="n">
-        <v>-3375138.51</v>
+        <v>-1119957.42</v>
       </c>
       <c r="V3" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W3" t="n">
-        <v>-1141352.84</v>
+        <v>-447647.26</v>
       </c>
       <c r="X3" t="n">
-        <v>3084347.8</v>
+        <v>1619436.88</v>
       </c>
       <c r="Y3" t="n">
-        <v>641544.34</v>
+        <v>424292.46</v>
       </c>
       <c r="Z3" t="n">
-        <v>2442803.46</v>
+        <v>1195144.42</v>
       </c>
       <c r="AA3" t="n">
-        <v>1850608.68</v>
+        <v>971662.13</v>
       </c>
       <c r="AB3" t="n">
-        <v>592194.78</v>
+        <v>223482.29</v>
       </c>
       <c r="AC3" t="n">
-        <v>11154625.45</v>
+        <v>5714211.73</v>
       </c>
       <c r="AD3" t="n">
-        <v>7957280.16</v>
+        <v>4135587.23</v>
       </c>
       <c r="AE3" t="n">
-        <v>3197345.29</v>
+        <v>1578624.5</v>
       </c>
     </row>
     <row r="4">
@@ -792,88 +780,88 @@
         <v>3</v>
       </c>
       <c r="D4" t="n">
-        <v>-2465380.98</v>
+        <v>-1502691.77</v>
       </c>
       <c r="E4" t="n">
-        <v>-290044.82</v>
+        <v>-176787.27</v>
       </c>
       <c r="F4" t="n">
-        <v>-145022.41</v>
+        <v>-88393.63</v>
       </c>
       <c r="G4" t="n">
-        <v>301646.61</v>
+        <v>231591.32</v>
       </c>
       <c r="H4" t="n">
-        <v>226234.96</v>
+        <v>173693.49</v>
       </c>
       <c r="I4" t="n">
-        <v>75411.64999999999</v>
+        <v>57897.83</v>
       </c>
       <c r="J4" t="n">
-        <v>725112.05</v>
+        <v>441968.17</v>
       </c>
       <c r="K4" t="n">
-        <v>580089.64</v>
+        <v>353574.53</v>
       </c>
       <c r="L4" t="n">
-        <v>435067.23</v>
+        <v>265180.9</v>
       </c>
       <c r="M4" t="n">
-        <v>58008.96</v>
+        <v>35357.45</v>
       </c>
       <c r="N4" t="n">
-        <v>4755305.71</v>
+        <v>2764544.78</v>
       </c>
       <c r="O4" t="n">
-        <v>58008.96</v>
+        <v>35357.45</v>
       </c>
       <c r="P4" t="n">
-        <v>6192649.24</v>
+        <v>3406503.44</v>
       </c>
       <c r="Q4" t="n">
-        <v>-91366.96000000001</v>
+        <v>-49449.24</v>
       </c>
       <c r="R4" t="n">
-        <v>-1115030.94</v>
+        <v>-883406.33</v>
       </c>
       <c r="S4" t="n">
-        <v>-87013.45</v>
+        <v>-53036.18</v>
       </c>
       <c r="T4" t="n">
-        <v>-2583851.5</v>
+        <v>-1500221.02</v>
       </c>
       <c r="U4" t="n">
-        <v>-3432478.69</v>
+        <v>-1933059.43</v>
       </c>
       <c r="V4" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W4" t="n">
-        <v>-1698238.9</v>
+        <v>-691613.6899999999</v>
       </c>
       <c r="X4" t="n">
-        <v>2900448.21</v>
+        <v>1767872.67</v>
       </c>
       <c r="Y4" t="n">
-        <v>603293.23</v>
+        <v>463182.64</v>
       </c>
       <c r="Z4" t="n">
-        <v>2297154.98</v>
+        <v>1304690.03</v>
       </c>
       <c r="AA4" t="n">
-        <v>1740268.93</v>
+        <v>1060723.6</v>
       </c>
       <c r="AB4" t="n">
-        <v>556886.0600000001</v>
+        <v>243966.43</v>
       </c>
       <c r="AC4" t="n">
-        <v>10972605.92</v>
+        <v>6192313.89</v>
       </c>
       <c r="AD4" t="n">
-        <v>7218374.58</v>
+        <v>4369722.96</v>
       </c>
       <c r="AE4" t="n">
-        <v>3754231.34</v>
+        <v>1822590.93</v>
       </c>
     </row>
     <row r="5">
@@ -889,88 +877,88 @@
         <v>4</v>
       </c>
       <c r="D5" t="n">
-        <v>-2793679.42</v>
+        <v>-1629848.44</v>
       </c>
       <c r="E5" t="n">
-        <v>-328668.17</v>
+        <v>-191746.87</v>
       </c>
       <c r="F5" t="n">
-        <v>-164334.08</v>
+        <v>-95873.44</v>
       </c>
       <c r="G5" t="n">
-        <v>341814.89</v>
+        <v>251188.41</v>
       </c>
       <c r="H5" t="n">
-        <v>256361.17</v>
+        <v>188391.3</v>
       </c>
       <c r="I5" t="n">
-        <v>85453.72</v>
+        <v>62797.1</v>
       </c>
       <c r="J5" t="n">
-        <v>821670.42</v>
+        <v>479367.19</v>
       </c>
       <c r="K5" t="n">
-        <v>657336.33</v>
+        <v>383493.75</v>
       </c>
       <c r="L5" t="n">
-        <v>493002.25</v>
+        <v>287620.31</v>
       </c>
       <c r="M5" t="n">
-        <v>65733.63</v>
+        <v>38349.37</v>
       </c>
       <c r="N5" t="n">
-        <v>4400624.66</v>
+        <v>3161109.21</v>
       </c>
       <c r="O5" t="n">
-        <v>65733.63</v>
+        <v>38349.37</v>
       </c>
       <c r="P5" t="n">
-        <v>6204985.2</v>
+        <v>3413289.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>-122065.28</v>
+        <v>-66063.66</v>
       </c>
       <c r="R5" t="n">
-        <v>-1200771.37</v>
+        <v>-750410.97</v>
       </c>
       <c r="S5" t="n">
-        <v>-98600.45</v>
+        <v>-57524.06</v>
       </c>
       <c r="T5" t="n">
-        <v>-3470317.06</v>
+        <v>-1816707.85</v>
       </c>
       <c r="U5" t="n">
-        <v>-1460048.74</v>
+        <v>-1873189.1</v>
       </c>
       <c r="V5" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W5" t="n">
-        <v>-2329281.78</v>
+        <v>-956224.38</v>
       </c>
       <c r="X5" t="n">
-        <v>3286681.67</v>
+        <v>1917468.75</v>
       </c>
       <c r="Y5" t="n">
-        <v>683629.79</v>
+        <v>502376.81</v>
       </c>
       <c r="Z5" t="n">
-        <v>2603051.89</v>
+        <v>1415091.94</v>
       </c>
       <c r="AA5" t="n">
-        <v>1972009</v>
+        <v>1150481.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>631042.88</v>
+        <v>264610.69</v>
       </c>
       <c r="AC5" t="n">
-        <v>10615011.84</v>
+        <v>6585033.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>6229737.62</v>
+        <v>4497831.99</v>
       </c>
       <c r="AE5" t="n">
-        <v>4385274.22</v>
+        <v>2087201.61</v>
       </c>
     </row>
     <row r="6">
@@ -986,88 +974,88 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>-2846670.7</v>
+        <v>-1633490.27</v>
       </c>
       <c r="E6" t="n">
-        <v>-334902.44</v>
+        <v>-192175.33</v>
       </c>
       <c r="F6" t="n">
-        <v>-167451.22</v>
+        <v>-96087.66</v>
       </c>
       <c r="G6" t="n">
-        <v>348298.53</v>
+        <v>251749.68</v>
       </c>
       <c r="H6" t="n">
-        <v>261223.9</v>
+        <v>188812.26</v>
       </c>
       <c r="I6" t="n">
-        <v>87074.63</v>
+        <v>62937.42</v>
       </c>
       <c r="J6" t="n">
-        <v>837256.09</v>
+        <v>480438.32</v>
       </c>
       <c r="K6" t="n">
-        <v>669804.87</v>
+        <v>384350.65</v>
       </c>
       <c r="L6" t="n">
-        <v>502353.65</v>
+        <v>288262.99</v>
       </c>
       <c r="M6" t="n">
-        <v>66980.49000000001</v>
+        <v>38435.07</v>
       </c>
       <c r="N6" t="n">
-        <v>5509573.25</v>
+        <v>3025339.06</v>
       </c>
       <c r="O6" t="n">
-        <v>66980.49000000001</v>
+        <v>38435.07</v>
       </c>
       <c r="P6" t="n">
-        <v>6217321.15</v>
+        <v>3420075.17</v>
       </c>
       <c r="Q6" t="n">
-        <v>-152884.95</v>
+        <v>-82743.75</v>
       </c>
       <c r="R6" t="n">
-        <v>-1088543.67</v>
+        <v>-815320.5600000001</v>
       </c>
       <c r="S6" t="n">
-        <v>-100470.73</v>
+        <v>-57652.6</v>
       </c>
       <c r="T6" t="n">
-        <v>-2779063.49</v>
+        <v>-1933296.81</v>
       </c>
       <c r="U6" t="n">
-        <v>-2711605.63</v>
+        <v>-1280867.06</v>
       </c>
       <c r="V6" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W6" t="n">
-        <v>-2972294.46</v>
+        <v>-1221426.33</v>
       </c>
       <c r="X6" t="n">
-        <v>3349024.36</v>
+        <v>1921753.26</v>
       </c>
       <c r="Y6" t="n">
-        <v>696597.0699999999</v>
+        <v>503499.35</v>
       </c>
       <c r="Z6" t="n">
-        <v>2652427.29</v>
+        <v>1418253.91</v>
       </c>
       <c r="AA6" t="n">
-        <v>2009414.61</v>
+        <v>1153051.96</v>
       </c>
       <c r="AB6" t="n">
-        <v>643012.6800000001</v>
+        <v>265201.95</v>
       </c>
       <c r="AC6" t="n">
-        <v>11707970.43</v>
+        <v>6439540.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>6679683.53</v>
+        <v>4087137.04</v>
       </c>
       <c r="AE6" t="n">
-        <v>5028286.9</v>
+        <v>2352403.56</v>
       </c>
     </row>
     <row r="7">
@@ -1083,86 +1071,88 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>-2999501.38</v>
+        <v>-1649975.33</v>
       </c>
       <c r="E7" t="n">
-        <v>-352882.52</v>
+        <v>-194114.74</v>
       </c>
       <c r="F7" t="n">
-        <v>-176441.26</v>
+        <v>-97057.37</v>
       </c>
       <c r="G7" t="n">
-        <v>366997.82</v>
+        <v>254290.32</v>
       </c>
       <c r="H7" t="n">
-        <v>275248.36</v>
+        <v>190717.74</v>
       </c>
       <c r="I7" t="n">
-        <v>91749.45</v>
+        <v>63572.58</v>
       </c>
       <c r="J7" t="n">
-        <v>882206.29</v>
+        <v>485286.86</v>
       </c>
       <c r="K7" t="n">
-        <v>705765.03</v>
+        <v>388229.49</v>
       </c>
       <c r="L7" t="n">
-        <v>529323.77</v>
+        <v>291172.12</v>
       </c>
       <c r="M7" t="n">
-        <v>480389.62</v>
+        <v>38822.95</v>
       </c>
       <c r="N7" t="n">
-        <v>5150250.43</v>
+        <v>3224199.57</v>
       </c>
       <c r="O7" t="n">
-        <v>70576.5</v>
+        <v>38822.95</v>
       </c>
       <c r="P7" t="n">
-        <v>6229657.11</v>
+        <v>3426861.03</v>
       </c>
       <c r="Q7" t="n">
-        <v>-183825.95</v>
+        <v>-99489.50999999999</v>
       </c>
       <c r="R7" t="n">
-        <v>-1438804.62</v>
+        <v>-947195.67</v>
       </c>
       <c r="S7" t="n">
-        <v>-105864.75</v>
+        <v>-58234.42</v>
       </c>
       <c r="T7" t="n">
-        <v>-4496557</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
+        <v>-2196243.13</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-807261.85</v>
+      </c>
       <c r="V7" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W7" t="n">
-        <v>-3649828.89</v>
+        <v>-1489304.67</v>
       </c>
       <c r="X7" t="n">
-        <v>3528825.15</v>
+        <v>1941147.44</v>
       </c>
       <c r="Y7" t="n">
-        <v>733995.63</v>
+        <v>508580.63</v>
       </c>
       <c r="Z7" t="n">
-        <v>2794829.52</v>
+        <v>1432566.81</v>
       </c>
       <c r="AA7" t="n">
-        <v>2117295.09</v>
+        <v>1164688.47</v>
       </c>
       <c r="AB7" t="n">
-        <v>677534.4300000001</v>
+        <v>267878.35</v>
       </c>
       <c r="AC7" t="n">
-        <v>11747047.71</v>
+        <v>6629216.99</v>
       </c>
       <c r="AD7" t="n">
-        <v>6041226.38</v>
+        <v>4008935.08</v>
       </c>
       <c r="AE7" t="n">
-        <v>5705821.33</v>
+        <v>2620281.91</v>
       </c>
     </row>
     <row r="8">
@@ -1178,86 +1168,86 @@
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>-3218866.03</v>
+        <v>-1841405.59</v>
       </c>
       <c r="E8" t="n">
-        <v>-378690.12</v>
+        <v>-216635.95</v>
       </c>
       <c r="F8" t="n">
-        <v>-189345.06</v>
+        <v>-108317.98</v>
       </c>
       <c r="G8" t="n">
-        <v>393837.73</v>
+        <v>283793.1</v>
       </c>
       <c r="H8" t="n">
-        <v>295378.29</v>
+        <v>212844.82</v>
       </c>
       <c r="I8" t="n">
-        <v>98459.42999999999</v>
+        <v>70948.27</v>
       </c>
       <c r="J8" t="n">
-        <v>946725.3</v>
+        <v>541589.88</v>
       </c>
       <c r="K8" t="n">
-        <v>757380.24</v>
+        <v>433271.9</v>
       </c>
       <c r="L8" t="n">
-        <v>568035.1800000001</v>
+        <v>324953.93</v>
       </c>
       <c r="M8" t="n">
-        <v>1444116.49</v>
+        <v>271205.16</v>
       </c>
       <c r="N8" t="n">
-        <v>5085938.77</v>
+        <v>2923729.98</v>
       </c>
       <c r="O8" t="n">
-        <v>75738.02</v>
+        <v>43327.19</v>
       </c>
       <c r="P8" t="n">
-        <v>6241993.06</v>
+        <v>3433646.89</v>
       </c>
       <c r="Q8" t="n">
-        <v>-214888.29</v>
+        <v>-116300.94</v>
       </c>
       <c r="R8" t="n">
-        <v>-1633371.99</v>
+        <v>-925724.33</v>
       </c>
       <c r="S8" t="n">
-        <v>-113607.04</v>
+        <v>-64990.79</v>
       </c>
       <c r="T8" t="n">
-        <v>-4453012.67</v>
+        <v>-2645653.64</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W8" t="n">
-        <v>-4376913.92</v>
+        <v>-1788262.29</v>
       </c>
       <c r="X8" t="n">
-        <v>3786901.21</v>
+        <v>2166359.52</v>
       </c>
       <c r="Y8" t="n">
-        <v>787675.45</v>
+        <v>567586.1899999999</v>
       </c>
       <c r="Z8" t="n">
-        <v>2999225.76</v>
+        <v>1598773.32</v>
       </c>
       <c r="AA8" t="n">
-        <v>2272140.73</v>
+        <v>1299815.71</v>
       </c>
       <c r="AB8" t="n">
-        <v>727085.03</v>
+        <v>298957.61</v>
       </c>
       <c r="AC8" t="n">
-        <v>12632898.06</v>
+        <v>6555608.28</v>
       </c>
       <c r="AD8" t="n">
-        <v>6199991.7</v>
+        <v>3636368.76</v>
       </c>
       <c r="AE8" t="n">
-        <v>6432906.36</v>
+        <v>2919239.52</v>
       </c>
     </row>
     <row r="9">
@@ -1273,86 +1263,86 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>-3160318.11</v>
+        <v>-1749431.39</v>
       </c>
       <c r="E9" t="n">
-        <v>-371802.13</v>
+        <v>-205815.46</v>
       </c>
       <c r="F9" t="n">
-        <v>-185901.07</v>
+        <v>-102907.73</v>
       </c>
       <c r="G9" t="n">
-        <v>386674.22</v>
+        <v>269618.25</v>
       </c>
       <c r="H9" t="n">
-        <v>290005.66</v>
+        <v>202213.69</v>
       </c>
       <c r="I9" t="n">
-        <v>96668.55</v>
+        <v>67404.56</v>
       </c>
       <c r="J9" t="n">
-        <v>929505.33</v>
+        <v>514538.64</v>
       </c>
       <c r="K9" t="n">
-        <v>743604.26</v>
+        <v>411630.92</v>
       </c>
       <c r="L9" t="n">
-        <v>557703.2</v>
+        <v>308723.19</v>
       </c>
       <c r="M9" t="n">
-        <v>289775.31</v>
+        <v>1010952.54</v>
       </c>
       <c r="N9" t="n">
-        <v>5717669.78</v>
+        <v>2774784.58</v>
       </c>
       <c r="O9" t="n">
-        <v>74360.42999999999</v>
+        <v>41163.09</v>
       </c>
       <c r="P9" t="n">
-        <v>6254329.02</v>
+        <v>3440432.76</v>
       </c>
       <c r="Q9" t="n">
-        <v>-246071.96</v>
+        <v>-133178.04</v>
       </c>
       <c r="R9" t="n">
-        <v>-1237469.87</v>
+        <v>-847372.13</v>
       </c>
       <c r="S9" t="n">
-        <v>-111540.64</v>
+        <v>-61744.64</v>
       </c>
       <c r="T9" t="n">
-        <v>-3594285.6</v>
+        <v>-3021773.3</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W9" t="n">
-        <v>-5090774.01</v>
+        <v>-2072287.62</v>
       </c>
       <c r="X9" t="n">
-        <v>3718021.3</v>
+        <v>2058154.58</v>
       </c>
       <c r="Y9" t="n">
-        <v>773348.4300000001</v>
+        <v>539236.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>2944672.87</v>
+        <v>1518918.08</v>
       </c>
       <c r="AA9" t="n">
-        <v>2230812.78</v>
+        <v>1234892.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>713860.09</v>
+        <v>284025.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>12090062.57</v>
+        <v>7134154.93</v>
       </c>
       <c r="AD9" t="n">
-        <v>4943296.12</v>
+        <v>3930890.07</v>
       </c>
       <c r="AE9" t="n">
-        <v>7146766.45</v>
+        <v>3203264.86</v>
       </c>
     </row>
     <row r="10">
@@ -1368,86 +1358,86 @@
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>-3367523.63</v>
+        <v>-1902023.86</v>
       </c>
       <c r="E10" t="n">
-        <v>-396179.25</v>
+        <v>-223767.51</v>
       </c>
       <c r="F10" t="n">
-        <v>-198089.63</v>
+        <v>-111883.76</v>
       </c>
       <c r="G10" t="n">
-        <v>412026.42</v>
+        <v>293135.44</v>
       </c>
       <c r="H10" t="n">
-        <v>309019.82</v>
+        <v>219851.58</v>
       </c>
       <c r="I10" t="n">
-        <v>103006.61</v>
+        <v>73283.86</v>
       </c>
       <c r="J10" t="n">
-        <v>990448.13</v>
+        <v>559418.78</v>
       </c>
       <c r="K10" t="n">
-        <v>792358.5</v>
+        <v>447535.03</v>
       </c>
       <c r="L10" t="n">
-        <v>594268.88</v>
+        <v>335651.27</v>
       </c>
       <c r="M10" t="n">
-        <v>3604446.53</v>
+        <v>1117449.2</v>
       </c>
       <c r="N10" t="n">
-        <v>5533368.47</v>
+        <v>3217152.87</v>
       </c>
       <c r="O10" t="n">
-        <v>79235.85000000001</v>
+        <v>44753.5</v>
       </c>
       <c r="P10" t="n">
-        <v>6266664.97</v>
+        <v>3447218.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>-277376.97</v>
+        <v>-150120.81</v>
       </c>
       <c r="R10" t="n">
-        <v>-1399394.83</v>
+        <v>-1051327</v>
       </c>
       <c r="S10" t="n">
-        <v>-118853.78</v>
+        <v>-67130.25</v>
       </c>
       <c r="T10" t="n">
-        <v>-5780659.62</v>
+        <v>-3045932.11</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W10" t="n">
-        <v>-5851438.17</v>
+        <v>-2381086.79</v>
       </c>
       <c r="X10" t="n">
-        <v>3961792.51</v>
+        <v>2237675.13</v>
       </c>
       <c r="Y10" t="n">
-        <v>824052.84</v>
+        <v>586270.88</v>
       </c>
       <c r="Z10" t="n">
-        <v>3137739.66</v>
+        <v>1651404.24</v>
       </c>
       <c r="AA10" t="n">
-        <v>2377075.5</v>
+        <v>1342605.08</v>
       </c>
       <c r="AB10" t="n">
-        <v>760664.16</v>
+        <v>308799.17</v>
       </c>
       <c r="AC10" t="n">
-        <v>15206338.84</v>
+        <v>7676453.38</v>
       </c>
       <c r="AD10" t="n">
-        <v>7298908.23</v>
+        <v>4164389.36</v>
       </c>
       <c r="AE10" t="n">
-        <v>7907430.61</v>
+        <v>3512064.02</v>
       </c>
     </row>
     <row r="11">
@@ -1463,86 +1453,86 @@
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>-3919720.75</v>
+        <v>-2091622.6</v>
       </c>
       <c r="E11" t="n">
-        <v>-461143.62</v>
+        <v>-246073.25</v>
       </c>
       <c r="F11" t="n">
-        <v>-230571.81</v>
+        <v>-123036.62</v>
       </c>
       <c r="G11" t="n">
-        <v>479589.36</v>
+        <v>322355.95</v>
       </c>
       <c r="H11" t="n">
-        <v>359692.02</v>
+        <v>241766.96</v>
       </c>
       <c r="I11" t="n">
-        <v>119897.34</v>
+        <v>80588.99000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>1152859.04</v>
+        <v>615183.12</v>
       </c>
       <c r="K11" t="n">
-        <v>922287.24</v>
+        <v>492146.49</v>
       </c>
       <c r="L11" t="n">
-        <v>691715.4300000001</v>
+        <v>369109.87</v>
       </c>
       <c r="M11" t="n">
-        <v>2594536.58</v>
+        <v>579582.22</v>
       </c>
       <c r="N11" t="n">
-        <v>6963719.49</v>
+        <v>4013111.94</v>
       </c>
       <c r="O11" t="n">
-        <v>92228.72</v>
+        <v>49214.65</v>
       </c>
       <c r="P11" t="n">
-        <v>6279000.93</v>
+        <v>3454004.48</v>
       </c>
       <c r="Q11" t="n">
-        <v>-308803.32</v>
+        <v>-167129.25</v>
       </c>
       <c r="R11" t="n">
-        <v>-1733033.63</v>
+        <v>-1022957.59</v>
       </c>
       <c r="S11" t="n">
-        <v>-138343.09</v>
+        <v>-73821.97</v>
       </c>
       <c r="T11" t="n">
-        <v>-4956479.31</v>
+        <v>-2980359.38</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W11" t="n">
-        <v>-6736833.92</v>
+        <v>-2720667.87</v>
       </c>
       <c r="X11" t="n">
-        <v>4611436.18</v>
+        <v>2460732.46</v>
       </c>
       <c r="Y11" t="n">
-        <v>959178.73</v>
+        <v>644711.91</v>
       </c>
       <c r="Z11" t="n">
-        <v>3652257.45</v>
+        <v>1816020.56</v>
       </c>
       <c r="AA11" t="n">
-        <v>2766861.71</v>
+        <v>1476439.48</v>
       </c>
       <c r="AB11" t="n">
-        <v>885395.75</v>
+        <v>339581.08</v>
       </c>
       <c r="AC11" t="n">
-        <v>15620682.39</v>
+        <v>7928784.05</v>
       </c>
       <c r="AD11" t="n">
-        <v>6827856.03</v>
+        <v>4077138.94</v>
       </c>
       <c r="AE11" t="n">
-        <v>8792826.359999999</v>
+        <v>3851645.1</v>
       </c>
     </row>
     <row r="12">
@@ -1558,86 +1548,86 @@
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>-3708340.2</v>
+        <v>-2207649.59</v>
       </c>
       <c r="E12" t="n">
-        <v>-436275.32</v>
+        <v>-259723.48</v>
       </c>
       <c r="F12" t="n">
-        <v>-218137.66</v>
+        <v>-129861.74</v>
       </c>
       <c r="G12" t="n">
-        <v>453726.33</v>
+        <v>340237.76</v>
       </c>
       <c r="H12" t="n">
-        <v>340294.75</v>
+        <v>255178.32</v>
       </c>
       <c r="I12" t="n">
-        <v>113431.58</v>
+        <v>85059.44</v>
       </c>
       <c r="J12" t="n">
-        <v>1090688.29</v>
+        <v>649308.7</v>
       </c>
       <c r="K12" t="n">
-        <v>872550.64</v>
+        <v>519446.96</v>
       </c>
       <c r="L12" t="n">
-        <v>654412.98</v>
+        <v>389585.22</v>
       </c>
       <c r="M12" t="n">
-        <v>3969855.89</v>
+        <v>1275447.67</v>
       </c>
       <c r="N12" t="n">
-        <v>7177547.28</v>
+        <v>3865678.06</v>
       </c>
       <c r="O12" t="n">
-        <v>87255.06</v>
+        <v>51944.7</v>
       </c>
       <c r="P12" t="n">
-        <v>6291336.88</v>
+        <v>3460790.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>-340351.01</v>
+        <v>-184203.36</v>
       </c>
       <c r="R12" t="n">
-        <v>-1614701.81</v>
+        <v>-987434.45</v>
       </c>
       <c r="S12" t="n">
-        <v>-130882.6</v>
+        <v>-77917.03999999999</v>
       </c>
       <c r="T12" t="n">
-        <v>-5809584.73</v>
+        <v>-3194242.41</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W12" t="n">
-        <v>-7574482.53</v>
+        <v>-3079086.27</v>
       </c>
       <c r="X12" t="n">
-        <v>4362753.18</v>
+        <v>2597234.81</v>
       </c>
       <c r="Y12" t="n">
-        <v>907452.66</v>
+        <v>680475.52</v>
       </c>
       <c r="Z12" t="n">
-        <v>3455300.52</v>
+        <v>1916759.29</v>
       </c>
       <c r="AA12" t="n">
-        <v>2617651.91</v>
+        <v>1558340.89</v>
       </c>
       <c r="AB12" t="n">
-        <v>837648.61</v>
+        <v>358418.4</v>
       </c>
       <c r="AC12" t="n">
-        <v>17185644.1</v>
+        <v>8469657.42</v>
       </c>
       <c r="AD12" t="n">
-        <v>7555169.13</v>
+        <v>4259593.91</v>
       </c>
       <c r="AE12" t="n">
-        <v>9630474.970000001</v>
+        <v>4210063.51</v>
       </c>
     </row>
     <row r="13">
@@ -1653,86 +1643,86 @@
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>-3566428.49</v>
+        <v>-2271529.76</v>
       </c>
       <c r="E13" t="n">
-        <v>-419579.82</v>
+        <v>-267238.8</v>
       </c>
       <c r="F13" t="n">
-        <v>-209789.91</v>
+        <v>-133619.4</v>
       </c>
       <c r="G13" t="n">
-        <v>436363.01</v>
+        <v>350082.82</v>
       </c>
       <c r="H13" t="n">
-        <v>327272.26</v>
+        <v>262562.12</v>
       </c>
       <c r="I13" t="n">
-        <v>109090.75</v>
+        <v>87520.71000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>1048949.56</v>
+        <v>668096.99</v>
       </c>
       <c r="K13" t="n">
-        <v>839159.64</v>
+        <v>534477.59</v>
       </c>
       <c r="L13" t="n">
-        <v>629369.73</v>
+        <v>400858.19</v>
       </c>
       <c r="M13" t="n">
-        <v>6036389.43</v>
+        <v>2278794.93</v>
       </c>
       <c r="N13" t="n">
-        <v>6102853.62</v>
+        <v>3944970.63</v>
       </c>
       <c r="O13" t="n">
-        <v>83915.96000000001</v>
+        <v>53447.76</v>
       </c>
       <c r="P13" t="n">
-        <v>6303672.84</v>
+        <v>3467576.21</v>
       </c>
       <c r="Q13" t="n">
-        <v>-372020.04</v>
+        <v>-201343.13</v>
       </c>
       <c r="R13" t="n">
-        <v>-1760429.06</v>
+        <v>-991313.83</v>
       </c>
       <c r="S13" t="n">
-        <v>-125873.95</v>
+        <v>-80171.64</v>
       </c>
       <c r="T13" t="n">
-        <v>-5832440.58</v>
+        <v>-3893107.89</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W13" t="n">
-        <v>-8380075.78</v>
+        <v>-3447875.81</v>
       </c>
       <c r="X13" t="n">
-        <v>4195798.22</v>
+        <v>2672387.95</v>
       </c>
       <c r="Y13" t="n">
-        <v>872726.03</v>
+        <v>700165.64</v>
       </c>
       <c r="Z13" t="n">
-        <v>3323072.19</v>
+        <v>1972222.31</v>
       </c>
       <c r="AA13" t="n">
-        <v>2517478.93</v>
+        <v>1603432.77</v>
       </c>
       <c r="AB13" t="n">
-        <v>805593.26</v>
+        <v>368789.54</v>
       </c>
       <c r="AC13" t="n">
-        <v>18154811.81</v>
+        <v>9543446.4</v>
       </c>
       <c r="AD13" t="n">
-        <v>7718743.58</v>
+        <v>4964593.35</v>
       </c>
       <c r="AE13" t="n">
-        <v>10436068.23</v>
+        <v>4578853.05</v>
       </c>
     </row>
     <row r="14">
@@ -1748,86 +1738,86 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-2848291.2</v>
+        <v>-1746081.63</v>
       </c>
       <c r="E14" t="n">
-        <v>-335093.08</v>
+        <v>-205421.37</v>
       </c>
       <c r="F14" t="n">
-        <v>-167546.54</v>
+        <v>-102710.68</v>
       </c>
       <c r="G14" t="n">
-        <v>348496.81</v>
+        <v>269101.99</v>
       </c>
       <c r="H14" t="n">
-        <v>261372.6</v>
+        <v>201826.49</v>
       </c>
       <c r="I14" t="n">
-        <v>87124.2</v>
+        <v>67275.5</v>
       </c>
       <c r="J14" t="n">
-        <v>837732.71</v>
+        <v>513553.42</v>
       </c>
       <c r="K14" t="n">
-        <v>670186.16</v>
+        <v>410842.74</v>
       </c>
       <c r="L14" t="n">
-        <v>502639.62</v>
+        <v>308132.05</v>
       </c>
       <c r="M14" t="n">
-        <v>4720698.5</v>
+        <v>1925490.65</v>
       </c>
       <c r="N14" t="n">
-        <v>5009495.16</v>
+        <v>2880680.33</v>
       </c>
       <c r="O14" t="n">
-        <v>67018.62</v>
+        <v>41084.27</v>
       </c>
       <c r="P14" t="n">
-        <v>6316008.79</v>
+        <v>3474362.07</v>
       </c>
       <c r="Q14" t="n">
-        <v>-403810.4</v>
+        <v>-218548.58</v>
       </c>
       <c r="R14" t="n">
-        <v>-1178416.03</v>
+        <v>-1043607.05</v>
       </c>
       <c r="S14" t="n">
-        <v>-100527.92</v>
+        <v>-61626.41</v>
       </c>
       <c r="T14" t="n">
-        <v>-3351019.76</v>
+        <v>-2135500.75</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W14" t="n">
-        <v>-9023454.5</v>
+        <v>-3731357.3</v>
       </c>
       <c r="X14" t="n">
-        <v>3350930.82</v>
+        <v>2054213.68</v>
       </c>
       <c r="Y14" t="n">
-        <v>696993.61</v>
+        <v>538203.98</v>
       </c>
       <c r="Z14" t="n">
-        <v>2653937.21</v>
+        <v>1516009.7</v>
       </c>
       <c r="AA14" t="n">
-        <v>2010558.49</v>
+        <v>1232528.21</v>
       </c>
       <c r="AB14" t="n">
-        <v>643378.72</v>
+        <v>283481.49</v>
       </c>
       <c r="AC14" t="n">
-        <v>15709410.66</v>
+        <v>8103068.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>4629963.72</v>
+        <v>3240734.21</v>
       </c>
       <c r="AE14" t="n">
-        <v>11079446.95</v>
+        <v>4862334.53</v>
       </c>
     </row>
     <row r="15">
@@ -1843,86 +1833,86 @@
         <v>2</v>
       </c>
       <c r="D15" t="n">
-        <v>-2941843.09</v>
+        <v>-1872895.64</v>
       </c>
       <c r="E15" t="n">
-        <v>-346099.19</v>
+        <v>-220340.66</v>
       </c>
       <c r="F15" t="n">
-        <v>-173049.59</v>
+        <v>-110170.33</v>
       </c>
       <c r="G15" t="n">
-        <v>359943.15</v>
+        <v>288646.27</v>
       </c>
       <c r="H15" t="n">
-        <v>269957.37</v>
+        <v>216484.7</v>
       </c>
       <c r="I15" t="n">
-        <v>89985.78999999999</v>
+        <v>72161.57000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>865247.97</v>
+        <v>550851.66</v>
       </c>
       <c r="K15" t="n">
-        <v>692198.37</v>
+        <v>440681.33</v>
       </c>
       <c r="L15" t="n">
-        <v>519148.78</v>
+        <v>330511</v>
       </c>
       <c r="M15" t="n">
-        <v>5069961.03</v>
+        <v>1647168.75</v>
       </c>
       <c r="N15" t="n">
-        <v>5564610.19</v>
+        <v>3385107.23</v>
       </c>
       <c r="O15" t="n">
-        <v>69219.84</v>
+        <v>44068.13</v>
       </c>
       <c r="P15" t="n">
-        <v>6328344.74</v>
+        <v>3481147.94</v>
       </c>
       <c r="Q15" t="n">
-        <v>-435722.1</v>
+        <v>-235819.7</v>
       </c>
       <c r="R15" t="n">
-        <v>-1487383.79</v>
+        <v>-1006619.88</v>
       </c>
       <c r="S15" t="n">
-        <v>-103829.76</v>
+        <v>-66102.2</v>
       </c>
       <c r="T15" t="n">
-        <v>-3261242.78</v>
+        <v>-2082545.62</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W15" t="n">
-        <v>-9687964.939999999</v>
+        <v>-4035427.41</v>
       </c>
       <c r="X15" t="n">
-        <v>3460991.87</v>
+        <v>2203406.64</v>
       </c>
       <c r="Y15" t="n">
-        <v>719886.3100000001</v>
+        <v>577292.54</v>
       </c>
       <c r="Z15" t="n">
-        <v>2741105.56</v>
+        <v>1626114.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2076595.12</v>
+        <v>1322043.98</v>
       </c>
       <c r="AB15" t="n">
-        <v>664510.4399999999</v>
+        <v>304070.12</v>
       </c>
       <c r="AC15" t="n">
-        <v>16596413.71</v>
+        <v>8321672.35</v>
       </c>
       <c r="AD15" t="n">
-        <v>4852456.32</v>
+        <v>3155267.7</v>
       </c>
       <c r="AE15" t="n">
-        <v>11743957.39</v>
+        <v>5166404.65</v>
       </c>
     </row>
     <row r="16">
@@ -1938,86 +1928,86 @@
         <v>3</v>
       </c>
       <c r="D16" t="n">
-        <v>-2830510.19</v>
+        <v>-1918058.58</v>
       </c>
       <c r="E16" t="n">
-        <v>-333001.2</v>
+        <v>-225653.95</v>
       </c>
       <c r="F16" t="n">
-        <v>-166500.6</v>
+        <v>-112826.98</v>
       </c>
       <c r="G16" t="n">
-        <v>346321.25</v>
+        <v>295606.68</v>
       </c>
       <c r="H16" t="n">
-        <v>259740.93</v>
+        <v>221705.01</v>
       </c>
       <c r="I16" t="n">
-        <v>86580.31</v>
+        <v>73901.67</v>
       </c>
       <c r="J16" t="n">
-        <v>832503</v>
+        <v>564134.88</v>
       </c>
       <c r="K16" t="n">
-        <v>666002.4</v>
+        <v>451307.9</v>
       </c>
       <c r="L16" t="n">
-        <v>499501.8</v>
+        <v>338480.93</v>
       </c>
       <c r="M16" t="n">
-        <v>6463214.06</v>
+        <v>1671217.01</v>
       </c>
       <c r="N16" t="n">
-        <v>4977042.64</v>
+        <v>3621561.97</v>
       </c>
       <c r="O16" t="n">
-        <v>66600.24000000001</v>
+        <v>45130.79</v>
       </c>
       <c r="P16" t="n">
-        <v>6340680.7</v>
+        <v>3487933.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>-467755.13</v>
+        <v>-253156.49</v>
       </c>
       <c r="R16" t="n">
-        <v>-1097304.31</v>
+        <v>-890970.6800000001</v>
       </c>
       <c r="S16" t="n">
-        <v>-99900.36</v>
+        <v>-67696.19</v>
       </c>
       <c r="T16" t="n">
-        <v>-3799258.15</v>
+        <v>-2136213.12</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W16" t="n">
-        <v>-10327327.24</v>
+        <v>-4346829.86</v>
       </c>
       <c r="X16" t="n">
-        <v>3330011.99</v>
+        <v>2256539.51</v>
       </c>
       <c r="Y16" t="n">
-        <v>692642.49</v>
+        <v>591213.35</v>
       </c>
       <c r="Z16" t="n">
-        <v>2637369.49</v>
+        <v>1665326.16</v>
       </c>
       <c r="AA16" t="n">
-        <v>1998007.19</v>
+        <v>1353923.7</v>
       </c>
       <c r="AB16" t="n">
-        <v>639362.3</v>
+        <v>311402.45</v>
       </c>
       <c r="AC16" t="n">
-        <v>17379782.51</v>
+        <v>8572687.08</v>
       </c>
       <c r="AD16" t="n">
-        <v>4996462.82</v>
+        <v>3094879.98</v>
       </c>
       <c r="AE16" t="n">
-        <v>12383319.69</v>
+        <v>5477807.1</v>
       </c>
     </row>
     <row r="17">
@@ -2033,86 +2023,86 @@
         <v>4</v>
       </c>
       <c r="D17" t="n">
-        <v>-3028406.21</v>
+        <v>-2135355.76</v>
       </c>
       <c r="E17" t="n">
-        <v>-356283.08</v>
+        <v>-251218.33</v>
       </c>
       <c r="F17" t="n">
-        <v>-178141.54</v>
+        <v>-125609.16</v>
       </c>
       <c r="G17" t="n">
-        <v>370534.41</v>
+        <v>329096.01</v>
       </c>
       <c r="H17" t="n">
-        <v>277900.8</v>
+        <v>246822</v>
       </c>
       <c r="I17" t="n">
-        <v>92633.60000000001</v>
+        <v>82274</v>
       </c>
       <c r="J17" t="n">
-        <v>890707.71</v>
+        <v>628045.8100000001</v>
       </c>
       <c r="K17" t="n">
-        <v>712566.17</v>
+        <v>502436.65</v>
       </c>
       <c r="L17" t="n">
-        <v>534424.62</v>
+        <v>376827.49</v>
       </c>
       <c r="M17" t="n">
-        <v>8207403.57</v>
+        <v>2325553.9</v>
       </c>
       <c r="N17" t="n">
-        <v>5209509.73</v>
+        <v>3995253.12</v>
       </c>
       <c r="O17" t="n">
-        <v>71256.62</v>
+        <v>50243.67</v>
       </c>
       <c r="P17" t="n">
-        <v>6353016.65</v>
+        <v>3494719.66</v>
       </c>
       <c r="Q17" t="n">
-        <v>-499909.51</v>
+        <v>-270558.94</v>
       </c>
       <c r="R17" t="n">
-        <v>-1519827.79</v>
+        <v>-1227807.5</v>
       </c>
       <c r="S17" t="n">
-        <v>-106884.92</v>
+        <v>-75365.5</v>
       </c>
       <c r="T17" t="n">
-        <v>-4647181.14</v>
+        <v>-2467550.02</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W17" t="n">
-        <v>-11011390.76</v>
+        <v>-4693511.15</v>
       </c>
       <c r="X17" t="n">
-        <v>3562830.83</v>
+        <v>2512183.25</v>
       </c>
       <c r="Y17" t="n">
-        <v>741068.8100000001</v>
+        <v>658192.01</v>
       </c>
       <c r="Z17" t="n">
-        <v>2821762.02</v>
+        <v>1853991.24</v>
       </c>
       <c r="AA17" t="n">
-        <v>2137698.5</v>
+        <v>1507309.95</v>
       </c>
       <c r="AB17" t="n">
-        <v>684063.52</v>
+        <v>346681.29</v>
       </c>
       <c r="AC17" t="n">
-        <v>19341277.06</v>
+        <v>9595211.41</v>
       </c>
       <c r="AD17" t="n">
-        <v>6273893.85</v>
+        <v>3770723.02</v>
       </c>
       <c r="AE17" t="n">
-        <v>13067383.21</v>
+        <v>5824488.39</v>
       </c>
     </row>
     <row r="18">
@@ -2128,86 +2118,86 @@
         <v>5</v>
       </c>
       <c r="D18" t="n">
-        <v>-3191857.02</v>
+        <v>-2124044.48</v>
       </c>
       <c r="E18" t="n">
-        <v>-375512.59</v>
+        <v>-249887.59</v>
       </c>
       <c r="F18" t="n">
-        <v>-187756.3</v>
+        <v>-124943.79</v>
       </c>
       <c r="G18" t="n">
-        <v>390533.09</v>
+        <v>327352.74</v>
       </c>
       <c r="H18" t="n">
-        <v>292899.82</v>
+        <v>245514.55</v>
       </c>
       <c r="I18" t="n">
-        <v>97633.27</v>
+        <v>81838.17999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>938781.48</v>
+        <v>624718.96</v>
       </c>
       <c r="K18" t="n">
-        <v>751025.1800000001</v>
+        <v>499775.17</v>
       </c>
       <c r="L18" t="n">
-        <v>563268.89</v>
+        <v>374831.38</v>
       </c>
       <c r="M18" t="n">
-        <v>7490158.07</v>
+        <v>3055991.14</v>
       </c>
       <c r="N18" t="n">
-        <v>5117743.84</v>
+        <v>3749456.33</v>
       </c>
       <c r="O18" t="n">
-        <v>75102.52</v>
+        <v>49977.52</v>
       </c>
       <c r="P18" t="n">
-        <v>6365352.61</v>
+        <v>3501505.53</v>
       </c>
       <c r="Q18" t="n">
-        <v>-532185.22</v>
+        <v>-288027.07</v>
       </c>
       <c r="R18" t="n">
-        <v>-1603574.28</v>
+        <v>-1260849.76</v>
       </c>
       <c r="S18" t="n">
-        <v>-112653.78</v>
+        <v>-74966.28</v>
       </c>
       <c r="T18" t="n">
-        <v>-3011576.38</v>
+        <v>-2563754.16</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W18" t="n">
-        <v>-11732374.94</v>
+        <v>-5038356.02</v>
       </c>
       <c r="X18" t="n">
-        <v>3755125.91</v>
+        <v>2498875.86</v>
       </c>
       <c r="Y18" t="n">
-        <v>781066.1899999999</v>
+        <v>654705.48</v>
       </c>
       <c r="Z18" t="n">
-        <v>2974059.72</v>
+        <v>1844170.38</v>
       </c>
       <c r="AA18" t="n">
-        <v>2253075.54</v>
+        <v>1499325.52</v>
       </c>
       <c r="AB18" t="n">
-        <v>720984.17</v>
+        <v>344844.87</v>
       </c>
       <c r="AC18" t="n">
-        <v>18516171.82</v>
+        <v>10068903.45</v>
       </c>
       <c r="AD18" t="n">
-        <v>4727804.44</v>
+        <v>3899570.19</v>
       </c>
       <c r="AE18" t="n">
-        <v>13788367.38</v>
+        <v>6169333.26</v>
       </c>
     </row>
     <row r="19">
@@ -2223,86 +2213,86 @@
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>-2984540.3</v>
+        <v>-2152104.7</v>
       </c>
       <c r="E19" t="n">
-        <v>-351122.39</v>
+        <v>-253188.79</v>
       </c>
       <c r="F19" t="n">
-        <v>-175561.19</v>
+        <v>-126594.39</v>
       </c>
       <c r="G19" t="n">
-        <v>365167.28</v>
+        <v>331677.31</v>
       </c>
       <c r="H19" t="n">
-        <v>273875.46</v>
+        <v>248757.98</v>
       </c>
       <c r="I19" t="n">
-        <v>91291.82000000001</v>
+        <v>82919.33</v>
       </c>
       <c r="J19" t="n">
-        <v>877805.97</v>
+        <v>632971.97</v>
       </c>
       <c r="K19" t="n">
-        <v>702244.78</v>
+        <v>506377.58</v>
       </c>
       <c r="L19" t="n">
-        <v>526683.58</v>
+        <v>379783.18</v>
       </c>
       <c r="M19" t="n">
-        <v>7809696.26</v>
+        <v>3681670.11</v>
       </c>
       <c r="N19" t="n">
-        <v>5559515.74</v>
+        <v>3979795.5</v>
       </c>
       <c r="O19" t="n">
-        <v>70224.48</v>
+        <v>50637.76</v>
       </c>
       <c r="P19" t="n">
-        <v>6377688.56</v>
+        <v>3508291.39</v>
       </c>
       <c r="Q19" t="n">
-        <v>-564582.27</v>
+        <v>-305560.86</v>
       </c>
       <c r="R19" t="n">
-        <v>-1532864.99</v>
+        <v>-1256445.81</v>
       </c>
       <c r="S19" t="n">
-        <v>-105336.72</v>
+        <v>-75956.64</v>
       </c>
       <c r="T19" t="n">
-        <v>-3151818.71</v>
+        <v>-3063697.67</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W19" t="n">
-        <v>-12406529.92</v>
+        <v>-5387756.55</v>
       </c>
       <c r="X19" t="n">
-        <v>3511223.88</v>
+        <v>2531887.88</v>
       </c>
       <c r="Y19" t="n">
-        <v>730334.5699999999</v>
+        <v>663354.63</v>
       </c>
       <c r="Z19" t="n">
-        <v>2780889.32</v>
+        <v>1868533.26</v>
       </c>
       <c r="AA19" t="n">
-        <v>2106734.33</v>
+        <v>1519132.73</v>
       </c>
       <c r="AB19" t="n">
-        <v>674154.99</v>
+        <v>349400.53</v>
       </c>
       <c r="AC19" t="n">
-        <v>19252542.78</v>
+        <v>10914833.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>4790020.41</v>
+        <v>4396100.11</v>
       </c>
       <c r="AE19" t="n">
-        <v>14462522.37</v>
+        <v>6518733.79</v>
       </c>
     </row>
     <row r="20">
@@ -2318,86 +2308,86 @@
         <v>7</v>
       </c>
       <c r="D20" t="n">
-        <v>-3118888.98</v>
+        <v>-2284528.43</v>
       </c>
       <c r="E20" t="n">
-        <v>-366928.11</v>
+        <v>-268768.05</v>
       </c>
       <c r="F20" t="n">
-        <v>-183464.06</v>
+        <v>-134384.03</v>
       </c>
       <c r="G20" t="n">
-        <v>381605.24</v>
+        <v>352086.15</v>
       </c>
       <c r="H20" t="n">
-        <v>286203.93</v>
+        <v>264064.61</v>
       </c>
       <c r="I20" t="n">
-        <v>95401.31</v>
+        <v>88021.53999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>917320.29</v>
+        <v>671920.13</v>
       </c>
       <c r="K20" t="n">
-        <v>733856.23</v>
+        <v>537536.1</v>
       </c>
       <c r="L20" t="n">
-        <v>550392.17</v>
+        <v>403152.08</v>
       </c>
       <c r="M20" t="n">
-        <v>9159523.880000001</v>
+        <v>2935629.12</v>
       </c>
       <c r="N20" t="n">
-        <v>5526185.75</v>
+        <v>4475964.28</v>
       </c>
       <c r="O20" t="n">
-        <v>73385.62</v>
+        <v>53753.61</v>
       </c>
       <c r="P20" t="n">
-        <v>6390024.52</v>
+        <v>3515077.25</v>
       </c>
       <c r="Q20" t="n">
-        <v>-597100.65</v>
+        <v>-323160.33</v>
       </c>
       <c r="R20" t="n">
-        <v>-1286394.64</v>
+        <v>-1057444.79</v>
       </c>
       <c r="S20" t="n">
-        <v>-110078.43</v>
+        <v>-80630.42</v>
       </c>
       <c r="T20" t="n">
-        <v>-3988521.69</v>
+        <v>-2629555.04</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W20" t="n">
-        <v>-13111031.9</v>
+        <v>-5758656.46</v>
       </c>
       <c r="X20" t="n">
-        <v>3669281.15</v>
+        <v>2687680.51</v>
       </c>
       <c r="Y20" t="n">
-        <v>763210.48</v>
+        <v>704172.29</v>
       </c>
       <c r="Z20" t="n">
-        <v>2906070.67</v>
+        <v>1983508.21</v>
       </c>
       <c r="AA20" t="n">
-        <v>2201568.69</v>
+        <v>1612608.3</v>
       </c>
       <c r="AB20" t="n">
-        <v>704501.98</v>
+        <v>370899.91</v>
       </c>
       <c r="AC20" t="n">
-        <v>20552019.12</v>
+        <v>10657263.94</v>
       </c>
       <c r="AD20" t="n">
-        <v>5384994.77</v>
+        <v>3767630.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>15167024.35</v>
+        <v>6889633.7</v>
       </c>
     </row>
     <row r="21">
@@ -2413,86 +2403,86 @@
         <v>8</v>
       </c>
       <c r="D21" t="n">
-        <v>-3248509.69</v>
+        <v>-2188312.85</v>
       </c>
       <c r="E21" t="n">
-        <v>-382177.61</v>
+        <v>-257448.57</v>
       </c>
       <c r="F21" t="n">
-        <v>-191088.81</v>
+        <v>-128724.29</v>
       </c>
       <c r="G21" t="n">
-        <v>397464.71</v>
+        <v>337257.63</v>
       </c>
       <c r="H21" t="n">
-        <v>298098.54</v>
+        <v>252943.22</v>
       </c>
       <c r="I21" t="n">
-        <v>99366.17999999999</v>
+        <v>84314.41</v>
       </c>
       <c r="J21" t="n">
-        <v>955444.03</v>
+        <v>643621.4300000001</v>
       </c>
       <c r="K21" t="n">
-        <v>764355.22</v>
+        <v>514897.14</v>
       </c>
       <c r="L21" t="n">
-        <v>573266.42</v>
+        <v>386172.86</v>
       </c>
       <c r="M21" t="n">
-        <v>8426825.800000001</v>
+        <v>3116414.21</v>
       </c>
       <c r="N21" t="n">
-        <v>6220206.92</v>
+        <v>4199950.05</v>
       </c>
       <c r="O21" t="n">
-        <v>76435.52</v>
+        <v>51489.71</v>
       </c>
       <c r="P21" t="n">
-        <v>6402360.47</v>
+        <v>3521863.12</v>
       </c>
       <c r="Q21" t="n">
-        <v>-629740.37</v>
+        <v>-340825.46</v>
       </c>
       <c r="R21" t="n">
-        <v>-1302060.48</v>
+        <v>-1040533.72</v>
       </c>
       <c r="S21" t="n">
-        <v>-114653.28</v>
+        <v>-77234.57000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-3178569.22</v>
+        <v>-2186210.62</v>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W21" t="n">
-        <v>-13844812.91</v>
+        <v>-6113935.48</v>
       </c>
       <c r="X21" t="n">
-        <v>3821776.1</v>
+        <v>2574485.7</v>
       </c>
       <c r="Y21" t="n">
-        <v>794929.4300000001</v>
+        <v>674515.25</v>
       </c>
       <c r="Z21" t="n">
-        <v>3026846.67</v>
+        <v>1899970.45</v>
       </c>
       <c r="AA21" t="n">
-        <v>2293065.66</v>
+        <v>1544691.42</v>
       </c>
       <c r="AB21" t="n">
-        <v>733781.01</v>
+        <v>355279.03</v>
       </c>
       <c r="AC21" t="n">
-        <v>20496088.34</v>
+        <v>10548891.63</v>
       </c>
       <c r="AD21" t="n">
-        <v>4595282.98</v>
+        <v>3303978.91</v>
       </c>
       <c r="AE21" t="n">
-        <v>15900805.36</v>
+        <v>7244912.72</v>
       </c>
     </row>
     <row r="22">
@@ -2508,86 +2498,86 @@
         <v>9</v>
       </c>
       <c r="D22" t="n">
-        <v>-3316065.47</v>
+        <v>-2321954.78</v>
       </c>
       <c r="E22" t="n">
-        <v>-390125.35</v>
+        <v>-273171.15</v>
       </c>
       <c r="F22" t="n">
-        <v>-195062.67</v>
+        <v>-136585.58</v>
       </c>
       <c r="G22" t="n">
-        <v>405730.36</v>
+        <v>357854.21</v>
       </c>
       <c r="H22" t="n">
-        <v>304297.77</v>
+        <v>268390.66</v>
       </c>
       <c r="I22" t="n">
-        <v>101432.59</v>
+        <v>89463.55</v>
       </c>
       <c r="J22" t="n">
-        <v>975313.37</v>
+        <v>682927.88</v>
       </c>
       <c r="K22" t="n">
-        <v>780250.7</v>
+        <v>546342.3</v>
       </c>
       <c r="L22" t="n">
-        <v>585188.02</v>
+        <v>409756.73</v>
       </c>
       <c r="M22" t="n">
-        <v>12172599.71</v>
+        <v>4727314.96</v>
       </c>
       <c r="N22" t="n">
-        <v>5503221.39</v>
+        <v>4343299.8</v>
       </c>
       <c r="O22" t="n">
-        <v>78025.07000000001</v>
+        <v>54634.23</v>
       </c>
       <c r="P22" t="n">
-        <v>6414696.43</v>
+        <v>3528648.98</v>
       </c>
       <c r="Q22" t="n">
-        <v>-662501.4300000001</v>
+        <v>-358556.27</v>
       </c>
       <c r="R22" t="n">
-        <v>-1281388.45</v>
+        <v>-1382337.41</v>
       </c>
       <c r="S22" t="n">
-        <v>-117037.6</v>
+        <v>-81951.35000000001</v>
       </c>
       <c r="T22" t="n">
-        <v>-5457769.08</v>
+        <v>-3209164.04</v>
       </c>
       <c r="U22" t="inlineStr"/>
       <c r="V22" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W22" t="n">
-        <v>-14593853.59</v>
+        <v>-6490911.67</v>
       </c>
       <c r="X22" t="n">
-        <v>3901253.49</v>
+        <v>2731711.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>811460.73</v>
+        <v>715708.41</v>
       </c>
       <c r="Z22" t="n">
-        <v>3089792.77</v>
+        <v>2016003.09</v>
       </c>
       <c r="AA22" t="n">
-        <v>2340752.1</v>
+        <v>1639026.9</v>
       </c>
       <c r="AB22" t="n">
-        <v>749040.67</v>
+        <v>376976.19</v>
       </c>
       <c r="AC22" t="n">
-        <v>23506041.16</v>
+        <v>12295341.71</v>
       </c>
       <c r="AD22" t="n">
-        <v>6856195.13</v>
+        <v>4673452.8</v>
       </c>
       <c r="AE22" t="n">
-        <v>16649846.03</v>
+        <v>7621888.91</v>
       </c>
     </row>
     <row r="23">
@@ -2603,86 +2593,86 @@
         <v>10</v>
       </c>
       <c r="D23" t="n">
-        <v>-3844900.87</v>
+        <v>-2956601.13</v>
       </c>
       <c r="E23" t="n">
-        <v>-452341.28</v>
+        <v>-347835.43</v>
       </c>
       <c r="F23" t="n">
-        <v>-226170.64</v>
+        <v>-173917.71</v>
       </c>
       <c r="G23" t="n">
-        <v>470434.93</v>
+        <v>455664.41</v>
       </c>
       <c r="H23" t="n">
-        <v>352826.2</v>
+        <v>341748.31</v>
       </c>
       <c r="I23" t="n">
-        <v>117608.73</v>
+        <v>113916.1</v>
       </c>
       <c r="J23" t="n">
-        <v>1130853.2</v>
+        <v>869588.5699999999</v>
       </c>
       <c r="K23" t="n">
-        <v>904682.5600000001</v>
+        <v>695670.86</v>
       </c>
       <c r="L23" t="n">
-        <v>678511.92</v>
+        <v>521753.14</v>
       </c>
       <c r="M23" t="n">
-        <v>11009718.31</v>
+        <v>4306038.8</v>
       </c>
       <c r="N23" t="n">
-        <v>6753026.19</v>
+        <v>5592230.8</v>
       </c>
       <c r="O23" t="n">
-        <v>90468.25999999999</v>
+        <v>69567.09</v>
       </c>
       <c r="P23" t="n">
-        <v>6427032.38</v>
+        <v>3535434.85</v>
       </c>
       <c r="Q23" t="n">
-        <v>-695383.83</v>
+        <v>-376352.74</v>
       </c>
       <c r="R23" t="n">
-        <v>-1968527.68</v>
+        <v>-1523670.14</v>
       </c>
       <c r="S23" t="n">
-        <v>-135702.38</v>
+        <v>-104350.63</v>
       </c>
       <c r="T23" t="n">
-        <v>-3962289.96</v>
+        <v>-3396996.22</v>
       </c>
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W23" t="n">
-        <v>-15462348.84</v>
+        <v>-6970924.56</v>
       </c>
       <c r="X23" t="n">
-        <v>4523412.78</v>
+        <v>3478354.28</v>
       </c>
       <c r="Y23" t="n">
-        <v>940869.86</v>
+        <v>911328.8199999999</v>
       </c>
       <c r="Z23" t="n">
-        <v>3582542.92</v>
+        <v>2567025.46</v>
       </c>
       <c r="AA23" t="n">
-        <v>2714047.67</v>
+        <v>2087012.57</v>
       </c>
       <c r="AB23" t="n">
-        <v>868495.25</v>
+        <v>480012.89</v>
       </c>
       <c r="AC23" t="n">
-        <v>23584861.31</v>
+        <v>13126918.79</v>
       </c>
       <c r="AD23" t="n">
-        <v>6066520.02</v>
+        <v>5025016.99</v>
       </c>
       <c r="AE23" t="n">
-        <v>17518341.28</v>
+        <v>8101901.8</v>
       </c>
     </row>
     <row r="24">
@@ -2698,86 +2688,86 @@
         <v>11</v>
       </c>
       <c r="D24" t="n">
-        <v>-3799975.3</v>
+        <v>-2811699.56</v>
       </c>
       <c r="E24" t="n">
-        <v>-447055.92</v>
+        <v>-330788.18</v>
       </c>
       <c r="F24" t="n">
-        <v>-223527.96</v>
+        <v>-165394.09</v>
       </c>
       <c r="G24" t="n">
-        <v>464938.15</v>
+        <v>433332.52</v>
       </c>
       <c r="H24" t="n">
-        <v>348703.62</v>
+        <v>324999.39</v>
       </c>
       <c r="I24" t="n">
-        <v>116234.54</v>
+        <v>108333.13</v>
       </c>
       <c r="J24" t="n">
-        <v>1117639.79</v>
+        <v>826970.46</v>
       </c>
       <c r="K24" t="n">
-        <v>894111.84</v>
+        <v>661576.37</v>
       </c>
       <c r="L24" t="n">
-        <v>670583.88</v>
+        <v>496182.28</v>
       </c>
       <c r="M24" t="n">
-        <v>13133335.81</v>
+        <v>5259520.21</v>
       </c>
       <c r="N24" t="n">
-        <v>7359636.69</v>
+        <v>5043672.15</v>
       </c>
       <c r="O24" t="n">
-        <v>89411.17999999999</v>
+        <v>66157.64</v>
       </c>
       <c r="P24" t="n">
-        <v>6439368.34</v>
+        <v>3542220.71</v>
       </c>
       <c r="Q24" t="n">
-        <v>-728387.5699999999</v>
+        <v>-394214.89</v>
       </c>
       <c r="R24" t="n">
-        <v>-1983679.12</v>
+        <v>-1459236.41</v>
       </c>
       <c r="S24" t="n">
-        <v>-134116.78</v>
+        <v>-99236.46000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>-5798879.91</v>
+        <v>-3400493.46</v>
       </c>
       <c r="U24" t="inlineStr"/>
       <c r="V24" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W24" t="n">
-        <v>-16320696.2</v>
+        <v>-7427412.26</v>
       </c>
       <c r="X24" t="n">
-        <v>4470559.18</v>
+        <v>3307881.84</v>
       </c>
       <c r="Y24" t="n">
-        <v>929876.3100000001</v>
+        <v>866665.04</v>
       </c>
       <c r="Z24" t="n">
-        <v>3540682.87</v>
+        <v>2441216.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>2682335.51</v>
+        <v>1984729.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>858347.36</v>
+        <v>456487.69</v>
       </c>
       <c r="AC24" t="n">
-        <v>26293364.46</v>
+        <v>13517355.82</v>
       </c>
       <c r="AD24" t="n">
-        <v>7916675.81</v>
+        <v>4958966.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>18376688.65</v>
+        <v>8558389.49</v>
       </c>
     </row>
     <row r="25">
@@ -2793,86 +2783,86 @@
         <v>12</v>
       </c>
       <c r="D25" t="n">
-        <v>-3696089.79</v>
+        <v>-2977636.74</v>
       </c>
       <c r="E25" t="n">
-        <v>-434834.09</v>
+        <v>-350310.2</v>
       </c>
       <c r="F25" t="n">
-        <v>-217417.05</v>
+        <v>-175155.1</v>
       </c>
       <c r="G25" t="n">
-        <v>452227.46</v>
+        <v>458906.37</v>
       </c>
       <c r="H25" t="n">
-        <v>339170.59</v>
+        <v>344179.78</v>
       </c>
       <c r="I25" t="n">
-        <v>113056.86</v>
+        <v>114726.59</v>
       </c>
       <c r="J25" t="n">
-        <v>1087085.23</v>
+        <v>875775.51</v>
       </c>
       <c r="K25" t="n">
-        <v>869668.1899999999</v>
+        <v>700620.41</v>
       </c>
       <c r="L25" t="n">
-        <v>652251.14</v>
+        <v>525465.3100000001</v>
       </c>
       <c r="M25" t="n">
-        <v>14458186.02</v>
+        <v>6353177.99</v>
       </c>
       <c r="N25" t="n">
-        <v>6483673.45</v>
+        <v>5329744.37</v>
       </c>
       <c r="O25" t="n">
-        <v>86966.82000000001</v>
+        <v>70062.03999999999</v>
       </c>
       <c r="P25" t="n">
-        <v>6451704.29</v>
+        <v>3549006.57</v>
       </c>
       <c r="Q25" t="n">
-        <v>-761512.64</v>
+        <v>-412142.7</v>
       </c>
       <c r="R25" t="n">
-        <v>-1919474.2</v>
+        <v>-1462286.08</v>
       </c>
       <c r="S25" t="n">
-        <v>-130450.23</v>
+        <v>-105093.06</v>
       </c>
       <c r="T25" t="n">
-        <v>-5457523.4</v>
+        <v>-4280651.56</v>
       </c>
       <c r="U25" t="inlineStr"/>
       <c r="V25" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W25" t="n">
-        <v>-17155577.66</v>
+        <v>-7910840.34</v>
       </c>
       <c r="X25" t="n">
-        <v>4348340.93</v>
+        <v>3503102.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>904454.91</v>
+        <v>917812.74</v>
       </c>
       <c r="Z25" t="n">
-        <v>3443886.01</v>
+        <v>2585289.31</v>
       </c>
       <c r="AA25" t="n">
-        <v>2609004.56</v>
+        <v>2101861.23</v>
       </c>
       <c r="AB25" t="n">
-        <v>834881.46</v>
+        <v>483428.08</v>
       </c>
       <c r="AC25" t="n">
-        <v>26719017.93</v>
+        <v>14889848.27</v>
       </c>
       <c r="AD25" t="n">
-        <v>7507447.83</v>
+        <v>5848030.7</v>
       </c>
       <c r="AE25" t="n">
-        <v>19211570.1</v>
+        <v>9041817.58</v>
       </c>
     </row>
     <row r="26">
@@ -2888,86 +2878,86 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2765000.28</v>
+        <v>-2287721.83</v>
       </c>
       <c r="E26" t="n">
-        <v>-325294.15</v>
+        <v>-269143.75</v>
       </c>
       <c r="F26" t="n">
-        <v>-162647.08</v>
+        <v>-134571.87</v>
       </c>
       <c r="G26" t="n">
-        <v>338305.92</v>
+        <v>352578.31</v>
       </c>
       <c r="H26" t="n">
-        <v>253729.44</v>
+        <v>264433.73</v>
       </c>
       <c r="I26" t="n">
-        <v>84576.48</v>
+        <v>88144.58</v>
       </c>
       <c r="J26" t="n">
-        <v>813235.38</v>
+        <v>672859.36</v>
       </c>
       <c r="K26" t="n">
-        <v>650588.3</v>
+        <v>538287.49</v>
       </c>
       <c r="L26" t="n">
-        <v>487941.23</v>
+        <v>403715.62</v>
       </c>
       <c r="M26" t="n">
-        <v>14485053.4</v>
+        <v>6562163.76</v>
       </c>
       <c r="N26" t="n">
-        <v>4523824.26</v>
+        <v>3966956.53</v>
       </c>
       <c r="O26" t="n">
-        <v>65058.83</v>
+        <v>53828.75</v>
       </c>
       <c r="P26" t="n">
-        <v>6464040.25</v>
+        <v>3555792.44</v>
       </c>
       <c r="Q26" t="n">
-        <v>-794759.05</v>
+        <v>-430136.18</v>
       </c>
       <c r="R26" t="n">
-        <v>-1295759.8</v>
+        <v>-1164398.4</v>
       </c>
       <c r="S26" t="n">
-        <v>-97588.25</v>
+        <v>-80743.12</v>
       </c>
       <c r="T26" t="n">
-        <v>-3513734.77</v>
+        <v>-3050227.82</v>
       </c>
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W26" t="n">
-        <v>-17780142.43</v>
+        <v>-8282258.71</v>
       </c>
       <c r="X26" t="n">
-        <v>3252941.51</v>
+        <v>2691437.45</v>
       </c>
       <c r="Y26" t="n">
-        <v>676611.83</v>
+        <v>705156.61</v>
       </c>
       <c r="Z26" t="n">
-        <v>2576329.67</v>
+        <v>1986280.84</v>
       </c>
       <c r="AA26" t="n">
-        <v>1951764.9</v>
+        <v>1614862.47</v>
       </c>
       <c r="AB26" t="n">
-        <v>624564.77</v>
+        <v>371418.37</v>
       </c>
       <c r="AC26" t="n">
-        <v>24743217.69</v>
+        <v>13708605.29</v>
       </c>
       <c r="AD26" t="n">
-        <v>4907082.82</v>
+        <v>4295369.34</v>
       </c>
       <c r="AE26" t="n">
-        <v>19836134.87</v>
+        <v>9413235.949999999</v>
       </c>
     </row>
     <row r="27">
@@ -2983,86 +2973,86 @@
         <v>2</v>
       </c>
       <c r="D27" t="n">
-        <v>-2971944.74</v>
+        <v>-2412472.67</v>
       </c>
       <c r="E27" t="n">
-        <v>-349640.56</v>
+        <v>-283820.31</v>
       </c>
       <c r="F27" t="n">
-        <v>-174820.28</v>
+        <v>-141910.16</v>
       </c>
       <c r="G27" t="n">
-        <v>363626.18</v>
+        <v>371804.61</v>
       </c>
       <c r="H27" t="n">
-        <v>272719.63</v>
+        <v>278853.46</v>
       </c>
       <c r="I27" t="n">
-        <v>90906.53999999999</v>
+        <v>92951.14999999999</v>
       </c>
       <c r="J27" t="n">
-        <v>874101.39</v>
+        <v>709550.79</v>
       </c>
       <c r="K27" t="n">
-        <v>699281.11</v>
+        <v>567640.63</v>
       </c>
       <c r="L27" t="n">
-        <v>524460.84</v>
+        <v>425730.47</v>
       </c>
       <c r="M27" t="n">
-        <v>14655087.47</v>
+        <v>6415586.22</v>
       </c>
       <c r="N27" t="n">
-        <v>5361016.35</v>
+        <v>4043032.39</v>
       </c>
       <c r="O27" t="n">
-        <v>69928.11</v>
+        <v>56764.06</v>
       </c>
       <c r="P27" t="n">
-        <v>6476376.2</v>
+        <v>3562578.3</v>
       </c>
       <c r="Q27" t="n">
-        <v>-828126.79</v>
+        <v>-448195.33</v>
       </c>
       <c r="R27" t="n">
-        <v>-1200792.32</v>
+        <v>-1335819.1</v>
       </c>
       <c r="S27" t="n">
-        <v>-104892.17</v>
+        <v>-85146.09</v>
       </c>
       <c r="T27" t="n">
-        <v>-3921152.11</v>
+        <v>-2403892.46</v>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W27" t="n">
-        <v>-18451452.3</v>
+        <v>-8673930.74</v>
       </c>
       <c r="X27" t="n">
-        <v>3496405.57</v>
+        <v>2838203.14</v>
       </c>
       <c r="Y27" t="n">
-        <v>727252.36</v>
+        <v>743609.22</v>
       </c>
       <c r="Z27" t="n">
-        <v>2769153.21</v>
+        <v>2094593.92</v>
       </c>
       <c r="AA27" t="n">
-        <v>2097843.34</v>
+        <v>1702921.89</v>
       </c>
       <c r="AB27" t="n">
-        <v>671309.87</v>
+        <v>391672.03</v>
       </c>
       <c r="AC27" t="n">
-        <v>25734281.33</v>
+        <v>13629765.63</v>
       </c>
       <c r="AD27" t="n">
-        <v>5226836.59</v>
+        <v>3824857.66</v>
       </c>
       <c r="AE27" t="n">
-        <v>20507444.74</v>
+        <v>9804907.98</v>
       </c>
     </row>
     <row r="28">
@@ -3078,86 +3068,86 @@
         <v>3</v>
       </c>
       <c r="D28" t="n">
-        <v>-3007073.4</v>
+        <v>-2361640.68</v>
       </c>
       <c r="E28" t="n">
-        <v>-353773.34</v>
+        <v>-277840.08</v>
       </c>
       <c r="F28" t="n">
-        <v>-176886.67</v>
+        <v>-138920.04</v>
       </c>
       <c r="G28" t="n">
-        <v>367924.28</v>
+        <v>363970.5</v>
       </c>
       <c r="H28" t="n">
-        <v>275943.21</v>
+        <v>272977.88</v>
       </c>
       <c r="I28" t="n">
-        <v>91981.07000000001</v>
+        <v>90992.63</v>
       </c>
       <c r="J28" t="n">
-        <v>884433.35</v>
+        <v>694600.2</v>
       </c>
       <c r="K28" t="n">
-        <v>707546.6800000001</v>
+        <v>555680.16</v>
       </c>
       <c r="L28" t="n">
-        <v>530660.01</v>
+        <v>416760.12</v>
       </c>
       <c r="M28" t="n">
-        <v>16680261.71</v>
+        <v>7483427.92</v>
       </c>
       <c r="N28" t="n">
-        <v>5390721.42</v>
+        <v>3863098.62</v>
       </c>
       <c r="O28" t="n">
-        <v>70754.67</v>
+        <v>55568.02</v>
       </c>
       <c r="P28" t="n">
-        <v>6488712.16</v>
+        <v>3569364.16</v>
       </c>
       <c r="Q28" t="n">
-        <v>-861615.88</v>
+        <v>-466320.16</v>
       </c>
       <c r="R28" t="n">
-        <v>-1555214.98</v>
+        <v>-1192652.49</v>
       </c>
       <c r="S28" t="n">
-        <v>-106132</v>
+        <v>-83352.02</v>
       </c>
       <c r="T28" t="n">
-        <v>-4920797.53</v>
+        <v>-3040806.75</v>
       </c>
       <c r="U28" t="inlineStr"/>
       <c r="V28" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W28" t="n">
-        <v>-19130697.11</v>
+        <v>-9057350.050000001</v>
       </c>
       <c r="X28" t="n">
-        <v>3537733.42</v>
+        <v>2778400.8</v>
       </c>
       <c r="Y28" t="n">
-        <v>735848.55</v>
+        <v>727941.01</v>
       </c>
       <c r="Z28" t="n">
-        <v>2801884.87</v>
+        <v>2050459.79</v>
       </c>
       <c r="AA28" t="n">
-        <v>2122640.05</v>
+        <v>1667040.48</v>
       </c>
       <c r="AB28" t="n">
-        <v>679244.8199999999</v>
+        <v>383419.31</v>
       </c>
       <c r="AC28" t="n">
-        <v>27768834.08</v>
+        <v>14505138.55</v>
       </c>
       <c r="AD28" t="n">
-        <v>6582144.52</v>
+        <v>4316811.26</v>
       </c>
       <c r="AE28" t="n">
-        <v>21186689.56</v>
+        <v>10188327.29</v>
       </c>
     </row>
     <row r="29">
@@ -3173,86 +3163,86 @@
         <v>4</v>
       </c>
       <c r="D29" t="n">
-        <v>-3301255.02</v>
+        <v>-2581948.29</v>
       </c>
       <c r="E29" t="n">
-        <v>-388382.94</v>
+        <v>-303758.62</v>
       </c>
       <c r="F29" t="n">
-        <v>-194191.47</v>
+        <v>-151879.31</v>
       </c>
       <c r="G29" t="n">
-        <v>403918.26</v>
+        <v>397923.79</v>
       </c>
       <c r="H29" t="n">
-        <v>302938.7</v>
+        <v>298442.85</v>
       </c>
       <c r="I29" t="n">
-        <v>100979.57</v>
+        <v>99480.95</v>
       </c>
       <c r="J29" t="n">
-        <v>970957.36</v>
+        <v>759396.55</v>
       </c>
       <c r="K29" t="n">
-        <v>776765.89</v>
+        <v>607517.24</v>
       </c>
       <c r="L29" t="n">
-        <v>582574.42</v>
+        <v>455637.93</v>
       </c>
       <c r="M29" t="n">
-        <v>16020957.08</v>
+        <v>7217302.73</v>
       </c>
       <c r="N29" t="n">
-        <v>5226646.73</v>
+        <v>4848848.72</v>
       </c>
       <c r="O29" t="n">
-        <v>77676.59</v>
+        <v>60751.72</v>
       </c>
       <c r="P29" t="n">
-        <v>6501048.11</v>
+        <v>3576150.03</v>
       </c>
       <c r="Q29" t="n">
-        <v>-895226.3</v>
+        <v>-484510.65</v>
       </c>
       <c r="R29" t="n">
-        <v>-1738666.27</v>
+        <v>-1295380.5</v>
       </c>
       <c r="S29" t="n">
-        <v>-116514.88</v>
+        <v>-91127.59</v>
       </c>
       <c r="T29" t="n">
-        <v>-3143536.24</v>
+        <v>-3224520.28</v>
       </c>
       <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W29" t="n">
-        <v>-19876392.37</v>
+        <v>-9476536.949999999</v>
       </c>
       <c r="X29" t="n">
-        <v>3883829.44</v>
+        <v>3037586.22</v>
       </c>
       <c r="Y29" t="n">
-        <v>807836.52</v>
+        <v>795847.59</v>
       </c>
       <c r="Z29" t="n">
-        <v>3075992.91</v>
+        <v>2241738.63</v>
       </c>
       <c r="AA29" t="n">
-        <v>2330297.66</v>
+        <v>1822551.73</v>
       </c>
       <c r="AB29" t="n">
-        <v>745695.25</v>
+        <v>419186.9</v>
       </c>
       <c r="AC29" t="n">
-        <v>26931102.21</v>
+        <v>15218542.56</v>
       </c>
       <c r="AD29" t="n">
-        <v>4998717.4</v>
+        <v>4611028.37</v>
       </c>
       <c r="AE29" t="n">
-        <v>21932384.81</v>
+        <v>10607514.19</v>
       </c>
     </row>
     <row r="30">
@@ -3268,86 +3258,86 @@
         <v>5</v>
       </c>
       <c r="D30" t="n">
-        <v>-3393814.19</v>
+        <v>-2556070.51</v>
       </c>
       <c r="E30" t="n">
-        <v>-399272.26</v>
+        <v>-300714.18</v>
       </c>
       <c r="F30" t="n">
-        <v>-199636.13</v>
+        <v>-150357.09</v>
       </c>
       <c r="G30" t="n">
-        <v>415243.15</v>
+        <v>393935.57</v>
       </c>
       <c r="H30" t="n">
-        <v>311432.36</v>
+        <v>295451.68</v>
       </c>
       <c r="I30" t="n">
-        <v>103810.79</v>
+        <v>98483.89</v>
       </c>
       <c r="J30" t="n">
-        <v>998180.64</v>
+        <v>751785.4399999999</v>
       </c>
       <c r="K30" t="n">
-        <v>798544.51</v>
+        <v>601428.35</v>
       </c>
       <c r="L30" t="n">
-        <v>598908.39</v>
+        <v>451071.27</v>
       </c>
       <c r="M30" t="n">
-        <v>18210723.41</v>
+        <v>9112600.67</v>
       </c>
       <c r="N30" t="n">
-        <v>5642526.68</v>
+        <v>4466130.85</v>
       </c>
       <c r="O30" t="n">
-        <v>79854.45</v>
+        <v>60142.84</v>
       </c>
       <c r="P30" t="n">
-        <v>6513384.06</v>
+        <v>3582935.89</v>
       </c>
       <c r="Q30" t="n">
-        <v>-928958.0600000001</v>
+        <v>-502766.81</v>
       </c>
       <c r="R30" t="n">
-        <v>-1490980.27</v>
+        <v>-1235833.76</v>
       </c>
       <c r="S30" t="n">
-        <v>-119781.68</v>
+        <v>-90214.25</v>
       </c>
       <c r="T30" t="n">
-        <v>-5207781.06</v>
+        <v>-4370495.66</v>
       </c>
       <c r="U30" t="inlineStr"/>
       <c r="V30" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W30" t="n">
-        <v>-20642995.1</v>
+        <v>-9891522.51</v>
       </c>
       <c r="X30" t="n">
-        <v>3992722.57</v>
+        <v>3007141.77</v>
       </c>
       <c r="Y30" t="n">
-        <v>830486.29</v>
+        <v>787871.14</v>
       </c>
       <c r="Z30" t="n">
-        <v>3162236.28</v>
+        <v>2219270.63</v>
       </c>
       <c r="AA30" t="n">
-        <v>2395633.54</v>
+        <v>1804285.06</v>
       </c>
       <c r="AB30" t="n">
-        <v>766602.73</v>
+        <v>414985.56</v>
       </c>
       <c r="AC30" t="n">
-        <v>29517530.55</v>
+        <v>16719043.43</v>
       </c>
       <c r="AD30" t="n">
-        <v>6818543</v>
+        <v>5696543.68</v>
       </c>
       <c r="AE30" t="n">
-        <v>22698987.55</v>
+        <v>11022499.75</v>
       </c>
     </row>
     <row r="31">
@@ -3363,86 +3353,86 @@
         <v>6</v>
       </c>
       <c r="D31" t="n">
-        <v>-3169256.86</v>
+        <v>-2466227.65</v>
       </c>
       <c r="E31" t="n">
-        <v>-372853.75</v>
+        <v>-290144.43</v>
       </c>
       <c r="F31" t="n">
-        <v>-186426.87</v>
+        <v>-145072.21</v>
       </c>
       <c r="G31" t="n">
-        <v>387767.9</v>
+        <v>380089.2</v>
       </c>
       <c r="H31" t="n">
-        <v>290825.92</v>
+        <v>285066.9</v>
       </c>
       <c r="I31" t="n">
-        <v>96941.97</v>
+        <v>95022.3</v>
       </c>
       <c r="J31" t="n">
-        <v>932134.37</v>
+        <v>725361.0699999999</v>
       </c>
       <c r="K31" t="n">
-        <v>745707.5</v>
+        <v>580288.86</v>
       </c>
       <c r="L31" t="n">
-        <v>559280.62</v>
+        <v>435216.64</v>
       </c>
       <c r="M31" t="n">
-        <v>18258052.33</v>
+        <v>9363202.970000001</v>
       </c>
       <c r="N31" t="n">
-        <v>5573500.08</v>
+        <v>4100750.77</v>
       </c>
       <c r="O31" t="n">
-        <v>74570.75</v>
+        <v>58028.89</v>
       </c>
       <c r="P31" t="n">
-        <v>6525720.02</v>
+        <v>3589721.75</v>
       </c>
       <c r="Q31" t="n">
-        <v>-962811.15</v>
+        <v>-521088.64</v>
       </c>
       <c r="R31" t="n">
-        <v>-1572494.4</v>
+        <v>-1260458.47</v>
       </c>
       <c r="S31" t="n">
-        <v>-111856.12</v>
+        <v>-87043.33</v>
       </c>
       <c r="T31" t="n">
-        <v>-4369814.75</v>
+        <v>-3820214.87</v>
       </c>
       <c r="U31" t="inlineStr"/>
       <c r="V31" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W31" t="n">
-        <v>-21358874.3</v>
+        <v>-10291921.83</v>
       </c>
       <c r="X31" t="n">
-        <v>3728537.48</v>
+        <v>2901444.3</v>
       </c>
       <c r="Y31" t="n">
-        <v>775535.8</v>
+        <v>760178.41</v>
       </c>
       <c r="Z31" t="n">
-        <v>2953001.68</v>
+        <v>2141265.89</v>
       </c>
       <c r="AA31" t="n">
-        <v>2237122.49</v>
+        <v>1740866.58</v>
       </c>
       <c r="AB31" t="n">
-        <v>715879.2</v>
+        <v>400399.31</v>
       </c>
       <c r="AC31" t="n">
-        <v>29469032.02</v>
+        <v>16590615.74</v>
       </c>
       <c r="AD31" t="n">
-        <v>6054165.28</v>
+        <v>5167716.67</v>
       </c>
       <c r="AE31" t="n">
-        <v>23414866.74</v>
+        <v>11422899.07</v>
       </c>
     </row>
     <row r="32">
@@ -3458,86 +3448,86 @@
         <v>7</v>
       </c>
       <c r="D32" t="n">
-        <v>-3382313.21</v>
+        <v>-2692601.12</v>
       </c>
       <c r="E32" t="n">
-        <v>-397919.2</v>
+        <v>-316776.6</v>
       </c>
       <c r="F32" t="n">
-        <v>-198959.6</v>
+        <v>-158388.3</v>
       </c>
       <c r="G32" t="n">
-        <v>413835.97</v>
+        <v>414977.35</v>
       </c>
       <c r="H32" t="n">
-        <v>310376.98</v>
+        <v>311233.01</v>
       </c>
       <c r="I32" t="n">
-        <v>103458.99</v>
+        <v>103744.34</v>
       </c>
       <c r="J32" t="n">
-        <v>994798</v>
+        <v>791941.51</v>
       </c>
       <c r="K32" t="n">
-        <v>795838.4</v>
+        <v>633553.2</v>
       </c>
       <c r="L32" t="n">
-        <v>596878.8</v>
+        <v>475164.9</v>
       </c>
       <c r="M32" t="n">
-        <v>18012243.75</v>
+        <v>8027917.37</v>
       </c>
       <c r="N32" t="n">
-        <v>6301941.04</v>
+        <v>5122756.28</v>
       </c>
       <c r="O32" t="n">
-        <v>79583.84</v>
+        <v>63355.32</v>
       </c>
       <c r="P32" t="n">
-        <v>6538055.97</v>
+        <v>3596507.62</v>
       </c>
       <c r="Q32" t="n">
-        <v>-996785.58</v>
+        <v>-539476.14</v>
       </c>
       <c r="R32" t="n">
-        <v>-1672541.27</v>
+        <v>-1380586.26</v>
       </c>
       <c r="S32" t="n">
-        <v>-119375.76</v>
+        <v>-95032.98</v>
       </c>
       <c r="T32" t="n">
-        <v>-3964250.39</v>
+        <v>-2935390.42</v>
       </c>
       <c r="U32" t="inlineStr"/>
       <c r="V32" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W32" t="n">
-        <v>-22122879.16</v>
+        <v>-10729073.54</v>
       </c>
       <c r="X32" t="n">
-        <v>3979192.01</v>
+        <v>3167766.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>827671.9399999999</v>
+        <v>829954.7</v>
       </c>
       <c r="Z32" t="n">
-        <v>3151520.07</v>
+        <v>2337811.32</v>
       </c>
       <c r="AA32" t="n">
-        <v>2387515.21</v>
+        <v>1900659.61</v>
       </c>
       <c r="AB32" t="n">
-        <v>764004.87</v>
+        <v>437151.71</v>
       </c>
       <c r="AC32" t="n">
-        <v>29935039.03</v>
+        <v>16271060.44</v>
       </c>
       <c r="AD32" t="n">
-        <v>5756167.42</v>
+        <v>4411009.66</v>
       </c>
       <c r="AE32" t="n">
-        <v>24178871.61</v>
+        <v>11860050.78</v>
       </c>
     </row>
     <row r="33">
@@ -3553,86 +3543,86 @@
         <v>8</v>
       </c>
       <c r="D33" t="n">
-        <v>-3462319.65</v>
+        <v>-2807775.24</v>
       </c>
       <c r="E33" t="n">
-        <v>-407331.72</v>
+        <v>-330326.5</v>
       </c>
       <c r="F33" t="n">
-        <v>-203665.86</v>
+        <v>-165163.25</v>
       </c>
       <c r="G33" t="n">
-        <v>423624.99</v>
+        <v>432727.71</v>
       </c>
       <c r="H33" t="n">
-        <v>317718.74</v>
+        <v>324545.79</v>
       </c>
       <c r="I33" t="n">
-        <v>105906.25</v>
+        <v>108181.93</v>
       </c>
       <c r="J33" t="n">
-        <v>1018329.31</v>
+        <v>825816.25</v>
       </c>
       <c r="K33" t="n">
-        <v>814663.45</v>
+        <v>660653</v>
       </c>
       <c r="L33" t="n">
-        <v>610997.59</v>
+        <v>495489.75</v>
       </c>
       <c r="M33" t="n">
-        <v>18575361.95</v>
+        <v>8830758</v>
       </c>
       <c r="N33" t="n">
-        <v>6683100.81</v>
+        <v>4686759.5</v>
       </c>
       <c r="O33" t="n">
-        <v>81466.34</v>
+        <v>66065.3</v>
       </c>
       <c r="P33" t="n">
-        <v>6550391.93</v>
+        <v>3603293.48</v>
       </c>
       <c r="Q33" t="n">
-        <v>-1030881.35</v>
+        <v>-557929.3100000001</v>
       </c>
       <c r="R33" t="n">
-        <v>-1500361.93</v>
+        <v>-1434759.65</v>
       </c>
       <c r="S33" t="n">
-        <v>-122199.52</v>
+        <v>-99097.95</v>
       </c>
       <c r="T33" t="n">
-        <v>-4275929.72</v>
+        <v>-2779188.01</v>
       </c>
       <c r="U33" t="inlineStr"/>
       <c r="V33" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W33" t="n">
-        <v>-22904956.07</v>
+        <v>-11184924.11</v>
       </c>
       <c r="X33" t="n">
-        <v>4073317.23</v>
+        <v>3303264.99</v>
       </c>
       <c r="Y33" t="n">
-        <v>847249.98</v>
+        <v>865455.4300000001</v>
       </c>
       <c r="Z33" t="n">
-        <v>3226067.25</v>
+        <v>2437809.56</v>
       </c>
       <c r="AA33" t="n">
-        <v>2443990.34</v>
+        <v>1981958.99</v>
       </c>
       <c r="AB33" t="n">
-        <v>782076.91</v>
+        <v>455850.57</v>
       </c>
       <c r="AC33" t="n">
-        <v>30859439.68</v>
+        <v>16628946.96</v>
       </c>
       <c r="AD33" t="n">
-        <v>5898491.17</v>
+        <v>4313045.62</v>
       </c>
       <c r="AE33" t="n">
-        <v>24960948.52</v>
+        <v>12315901.35</v>
       </c>
     </row>
     <row r="34">
@@ -3648,86 +3638,86 @@
         <v>9</v>
       </c>
       <c r="D34" t="n">
-        <v>-3381619.86</v>
+        <v>-2805384.79</v>
       </c>
       <c r="E34" t="n">
-        <v>-397837.63</v>
+        <v>-330045.27</v>
       </c>
       <c r="F34" t="n">
-        <v>-198918.82</v>
+        <v>-165022.63</v>
       </c>
       <c r="G34" t="n">
-        <v>413751.14</v>
+        <v>432359.3</v>
       </c>
       <c r="H34" t="n">
-        <v>310313.35</v>
+        <v>324269.48</v>
       </c>
       <c r="I34" t="n">
-        <v>103437.78</v>
+        <v>108089.83</v>
       </c>
       <c r="J34" t="n">
-        <v>994594.08</v>
+        <v>825113.17</v>
       </c>
       <c r="K34" t="n">
-        <v>795675.26</v>
+        <v>660090.54</v>
       </c>
       <c r="L34" t="n">
-        <v>596756.45</v>
+        <v>495067.9</v>
       </c>
       <c r="M34" t="n">
-        <v>19248542.83</v>
+        <v>9855850.289999999</v>
       </c>
       <c r="N34" t="n">
-        <v>6206459.49</v>
+        <v>5227091.71</v>
       </c>
       <c r="O34" t="n">
-        <v>79567.53</v>
+        <v>66009.05</v>
       </c>
       <c r="P34" t="n">
-        <v>6562727.88</v>
+        <v>3610079.34</v>
       </c>
       <c r="Q34" t="n">
-        <v>-1065098.46</v>
+        <v>-576448.15</v>
       </c>
       <c r="R34" t="n">
-        <v>-1731118.09</v>
+        <v>-1441664.78</v>
       </c>
       <c r="S34" t="n">
-        <v>-119351.29</v>
+        <v>-99013.58</v>
       </c>
       <c r="T34" t="n">
-        <v>-3456933.12</v>
+        <v>-3870540.07</v>
       </c>
       <c r="U34" t="inlineStr"/>
       <c r="V34" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W34" t="n">
-        <v>-23668804.32</v>
+        <v>-11640386.58</v>
       </c>
       <c r="X34" t="n">
-        <v>3978376.3</v>
+        <v>3300452.69</v>
       </c>
       <c r="Y34" t="n">
-        <v>827502.27</v>
+        <v>864718.61</v>
       </c>
       <c r="Z34" t="n">
-        <v>3150874.03</v>
+        <v>2435734.09</v>
       </c>
       <c r="AA34" t="n">
-        <v>2387025.78</v>
+        <v>1980271.62</v>
       </c>
       <c r="AB34" t="n">
-        <v>763848.25</v>
+        <v>455462.47</v>
       </c>
       <c r="AC34" t="n">
-        <v>31032199.27</v>
+        <v>18182582.25</v>
       </c>
       <c r="AD34" t="n">
-        <v>5307402.5</v>
+        <v>5411218.44</v>
       </c>
       <c r="AE34" t="n">
-        <v>25724796.77</v>
+        <v>12771363.82</v>
       </c>
     </row>
     <row r="35">
@@ -3743,86 +3733,86 @@
         <v>10</v>
       </c>
       <c r="D35" t="n">
-        <v>-4023322.61</v>
+        <v>-3260534.4</v>
       </c>
       <c r="E35" t="n">
-        <v>-473332.07</v>
+        <v>-383592.28</v>
       </c>
       <c r="F35" t="n">
-        <v>-236666.04</v>
+        <v>-191796.14</v>
       </c>
       <c r="G35" t="n">
-        <v>492265.35</v>
+        <v>502505.89</v>
       </c>
       <c r="H35" t="n">
-        <v>369199.02</v>
+        <v>376879.42</v>
       </c>
       <c r="I35" t="n">
-        <v>123066.34</v>
+        <v>125626.47</v>
       </c>
       <c r="J35" t="n">
-        <v>1183330.18</v>
+        <v>958980.71</v>
       </c>
       <c r="K35" t="n">
-        <v>946664.14</v>
+        <v>767184.5600000001</v>
       </c>
       <c r="L35" t="n">
-        <v>709998.11</v>
+        <v>575388.42</v>
       </c>
       <c r="M35" t="n">
-        <v>22974691.89</v>
+        <v>9577331.08</v>
       </c>
       <c r="N35" t="n">
-        <v>6481197.72</v>
+        <v>6340065.12</v>
       </c>
       <c r="O35" t="n">
-        <v>94666.41</v>
+        <v>76718.46000000001</v>
       </c>
       <c r="P35" t="n">
-        <v>6575063.84</v>
+        <v>3616865.21</v>
       </c>
       <c r="Q35" t="n">
-        <v>-1099436.9</v>
+        <v>-595032.66</v>
       </c>
       <c r="R35" t="n">
-        <v>-1650116.12</v>
+        <v>-1865987.15</v>
       </c>
       <c r="S35" t="n">
-        <v>-141999.62</v>
+        <v>-115077.68</v>
       </c>
       <c r="T35" t="n">
-        <v>-6600472.87</v>
+        <v>-3734161.2</v>
       </c>
       <c r="U35" t="inlineStr"/>
       <c r="V35" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W35" t="n">
-        <v>-24577601.9</v>
+        <v>-12169743.93</v>
       </c>
       <c r="X35" t="n">
-        <v>4733320.72</v>
+        <v>3835922.82</v>
       </c>
       <c r="Y35" t="n">
-        <v>984530.71</v>
+        <v>1005011.78</v>
       </c>
       <c r="Z35" t="n">
-        <v>3748790.01</v>
+        <v>2830911.04</v>
       </c>
       <c r="AA35" t="n">
-        <v>2839992.43</v>
+        <v>2301553.69</v>
       </c>
       <c r="AB35" t="n">
-        <v>908797.58</v>
+        <v>529357.35</v>
       </c>
       <c r="AC35" t="n">
-        <v>35026182.96</v>
+        <v>19015947.2</v>
       </c>
       <c r="AD35" t="n">
-        <v>8392588.609999999</v>
+        <v>5715226.03</v>
       </c>
       <c r="AE35" t="n">
-        <v>26633594.34</v>
+        <v>13300721.17</v>
       </c>
     </row>
     <row r="36">
@@ -3838,86 +3828,86 @@
         <v>11</v>
       </c>
       <c r="D36" t="n">
-        <v>-4077847.44</v>
+        <v>-3256180.88</v>
       </c>
       <c r="E36" t="n">
-        <v>-479746.76</v>
+        <v>-383080.1</v>
       </c>
       <c r="F36" t="n">
-        <v>-239873.38</v>
+        <v>-191540.05</v>
       </c>
       <c r="G36" t="n">
-        <v>498936.63</v>
+        <v>501834.93</v>
       </c>
       <c r="H36" t="n">
-        <v>374202.47</v>
+        <v>376376.2</v>
       </c>
       <c r="I36" t="n">
-        <v>124734.16</v>
+        <v>125458.73</v>
       </c>
       <c r="J36" t="n">
-        <v>1199366.89</v>
+        <v>957700.26</v>
       </c>
       <c r="K36" t="n">
-        <v>959493.52</v>
+        <v>766160.21</v>
       </c>
       <c r="L36" t="n">
-        <v>719620.14</v>
+        <v>574620.15</v>
       </c>
       <c r="M36" t="n">
-        <v>23661655.01</v>
+        <v>12428837.04</v>
       </c>
       <c r="N36" t="n">
-        <v>6451167.98</v>
+        <v>5368085.15</v>
       </c>
       <c r="O36" t="n">
-        <v>95949.35000000001</v>
+        <v>76616.02</v>
       </c>
       <c r="P36" t="n">
-        <v>6587399.79</v>
+        <v>3623651.07</v>
       </c>
       <c r="Q36" t="n">
-        <v>-1133896.69</v>
+        <v>-613682.84</v>
       </c>
       <c r="R36" t="n">
-        <v>-2057569.2</v>
+        <v>-1475564.56</v>
       </c>
       <c r="S36" t="n">
-        <v>-143924.03</v>
+        <v>-114924.03</v>
       </c>
       <c r="T36" t="n">
-        <v>-5906074.11</v>
+        <v>-5463646.13</v>
       </c>
       <c r="U36" t="inlineStr"/>
       <c r="V36" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W36" t="n">
-        <v>-25498715.67</v>
+        <v>-12698394.47</v>
       </c>
       <c r="X36" t="n">
-        <v>4797467.58</v>
+        <v>3830801.03</v>
       </c>
       <c r="Y36" t="n">
-        <v>997873.26</v>
+        <v>1003669.87</v>
       </c>
       <c r="Z36" t="n">
-        <v>3799594.32</v>
+        <v>2827131.16</v>
       </c>
       <c r="AA36" t="n">
-        <v>2878480.55</v>
+        <v>2298480.62</v>
       </c>
       <c r="AB36" t="n">
-        <v>921113.78</v>
+        <v>528650.54</v>
       </c>
       <c r="AC36" t="n">
-        <v>35662275.45</v>
+        <v>20883506.43</v>
       </c>
       <c r="AD36" t="n">
-        <v>8107567.33</v>
+        <v>7054134.72</v>
       </c>
       <c r="AE36" t="n">
-        <v>27554708.12</v>
+        <v>13829371.71</v>
       </c>
     </row>
     <row r="37">
@@ -3933,86 +3923,86 @@
         <v>12</v>
       </c>
       <c r="D37" t="n">
-        <v>-4017174.03</v>
+        <v>-3435543.4</v>
       </c>
       <c r="E37" t="n">
-        <v>-472608.71</v>
+        <v>-404181.58</v>
       </c>
       <c r="F37" t="n">
-        <v>-236304.35</v>
+        <v>-202090.79</v>
       </c>
       <c r="G37" t="n">
-        <v>491513.06</v>
+        <v>529477.86</v>
       </c>
       <c r="H37" t="n">
-        <v>368634.79</v>
+        <v>397108.4</v>
       </c>
       <c r="I37" t="n">
-        <v>122878.26</v>
+        <v>132369.47</v>
       </c>
       <c r="J37" t="n">
-        <v>1181521.77</v>
+        <v>1010453.94</v>
       </c>
       <c r="K37" t="n">
-        <v>945217.42</v>
+        <v>808363.15</v>
       </c>
       <c r="L37" t="n">
-        <v>708913.0600000001</v>
+        <v>606272.36</v>
       </c>
       <c r="M37" t="n">
-        <v>23547032.47</v>
+        <v>12140794.24</v>
       </c>
       <c r="N37" t="n">
-        <v>6911431.68</v>
+        <v>6328290.97</v>
       </c>
       <c r="O37" t="n">
-        <v>94521.74000000001</v>
+        <v>80836.32000000001</v>
       </c>
       <c r="P37" t="n">
-        <v>6599735.75</v>
+        <v>3630436.93</v>
       </c>
       <c r="Q37" t="n">
-        <v>-1168477.8</v>
+        <v>-632398.6899999999</v>
       </c>
       <c r="R37" t="n">
-        <v>-1845152.43</v>
+        <v>-1686794.4</v>
       </c>
       <c r="S37" t="n">
-        <v>-141782.61</v>
+        <v>-121254.47</v>
       </c>
       <c r="T37" t="n">
-        <v>-5535191.95</v>
+        <v>-5352768.61</v>
       </c>
       <c r="U37" t="inlineStr"/>
       <c r="V37" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W37" t="n">
-        <v>-26406124.4</v>
+        <v>-13256165.05</v>
       </c>
       <c r="X37" t="n">
-        <v>4726087.09</v>
+        <v>4041815.76</v>
       </c>
       <c r="Y37" t="n">
-        <v>983026.12</v>
+        <v>1058955.73</v>
       </c>
       <c r="Z37" t="n">
-        <v>3743060.98</v>
+        <v>2982860.03</v>
       </c>
       <c r="AA37" t="n">
-        <v>2835652.26</v>
+        <v>2425089.46</v>
       </c>
       <c r="AB37" t="n">
-        <v>907408.72</v>
+        <v>557770.5699999999</v>
       </c>
       <c r="AC37" t="n">
-        <v>35984243.83</v>
+        <v>21547959.77</v>
       </c>
       <c r="AD37" t="n">
-        <v>7522126.99</v>
+        <v>7160817.48</v>
       </c>
       <c r="AE37" t="n">
-        <v>28462116.84</v>
+        <v>14387142.28</v>
       </c>
     </row>
     <row r="38">
@@ -4028,86 +4018,86 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>-2887374.37</v>
+        <v>-2599367.85</v>
       </c>
       <c r="E38" t="n">
-        <v>-339691.1</v>
+        <v>-305807.98</v>
       </c>
       <c r="F38" t="n">
-        <v>-169845.55</v>
+        <v>-152903.99</v>
       </c>
       <c r="G38" t="n">
-        <v>353278.75</v>
+        <v>400608.46</v>
       </c>
       <c r="H38" t="n">
-        <v>264959.06</v>
+        <v>300456.34</v>
       </c>
       <c r="I38" t="n">
-        <v>88319.69</v>
+        <v>100152.11</v>
       </c>
       <c r="J38" t="n">
-        <v>849227.76</v>
+        <v>764519.95</v>
       </c>
       <c r="K38" t="n">
-        <v>679382.2</v>
+        <v>611615.96</v>
       </c>
       <c r="L38" t="n">
-        <v>509536.65</v>
+        <v>458711.97</v>
       </c>
       <c r="M38" t="n">
-        <v>25303687.54</v>
+        <v>11523790.64</v>
       </c>
       <c r="N38" t="n">
-        <v>4588631</v>
+        <v>4763099.24</v>
       </c>
       <c r="O38" t="n">
-        <v>67938.22</v>
+        <v>61161.6</v>
       </c>
       <c r="P38" t="n">
-        <v>6612071.7</v>
+        <v>3637222.8</v>
       </c>
       <c r="Q38" t="n">
-        <v>-1203180.26</v>
+        <v>-651180.21</v>
       </c>
       <c r="R38" t="n">
-        <v>-1194944.13</v>
+        <v>-1469396.19</v>
       </c>
       <c r="S38" t="n">
-        <v>-101907.33</v>
+        <v>-91742.39</v>
       </c>
       <c r="T38" t="n">
-        <v>-4957972.98</v>
+        <v>-2963798.18</v>
       </c>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W38" t="n">
-        <v>-27058331.31</v>
+        <v>-13678180.06</v>
       </c>
       <c r="X38" t="n">
-        <v>3396911.02</v>
+        <v>3058079.82</v>
       </c>
       <c r="Y38" t="n">
-        <v>706557.49</v>
+        <v>801216.91</v>
       </c>
       <c r="Z38" t="n">
-        <v>2690353.53</v>
+        <v>2256862.91</v>
       </c>
       <c r="AA38" t="n">
-        <v>2038146.61</v>
+        <v>1834847.89</v>
       </c>
       <c r="AB38" t="n">
-        <v>652206.92</v>
+        <v>422015.02</v>
       </c>
       <c r="AC38" t="n">
-        <v>35369148.19</v>
+        <v>19334094.06</v>
       </c>
       <c r="AD38" t="n">
-        <v>6254824.44</v>
+        <v>4524936.76</v>
       </c>
       <c r="AE38" t="n">
-        <v>29114323.76</v>
+        <v>14809157.3</v>
       </c>
     </row>
     <row r="39">
@@ -4123,86 +4113,86 @@
         <v>2</v>
       </c>
       <c r="D39" t="n">
-        <v>-3037355.05</v>
+        <v>-2588361.23</v>
       </c>
       <c r="E39" t="n">
-        <v>-357335.89</v>
+        <v>-304513.09</v>
       </c>
       <c r="F39" t="n">
-        <v>-178667.94</v>
+        <v>-152256.54</v>
       </c>
       <c r="G39" t="n">
-        <v>371629.32</v>
+        <v>398912.14</v>
       </c>
       <c r="H39" t="n">
-        <v>278721.99</v>
+        <v>299184.11</v>
       </c>
       <c r="I39" t="n">
-        <v>92907.33</v>
+        <v>99728.03999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>893339.72</v>
+        <v>761282.71</v>
       </c>
       <c r="K39" t="n">
-        <v>714671.78</v>
+        <v>609026.17</v>
       </c>
       <c r="L39" t="n">
-        <v>536003.83</v>
+        <v>456769.63</v>
       </c>
       <c r="M39" t="n">
-        <v>24114734.81</v>
+        <v>13161888.39</v>
       </c>
       <c r="N39" t="n">
-        <v>5148608.78</v>
+        <v>4355884.87</v>
       </c>
       <c r="O39" t="n">
-        <v>71467.17999999999</v>
+        <v>60902.62</v>
       </c>
       <c r="P39" t="n">
-        <v>6624407.66</v>
+        <v>3644008.66</v>
       </c>
       <c r="Q39" t="n">
-        <v>-1238004.05</v>
+        <v>-670027.4</v>
       </c>
       <c r="R39" t="n">
-        <v>-1287930.68</v>
+        <v>-1293907.48</v>
       </c>
       <c r="S39" t="n">
-        <v>-107200.77</v>
+        <v>-91353.92999999999</v>
       </c>
       <c r="T39" t="n">
-        <v>-3525674.26</v>
+        <v>-3938010.37</v>
       </c>
       <c r="U39" t="inlineStr"/>
       <c r="V39" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W39" t="n">
-        <v>-27744416.22</v>
+        <v>-14098408.12</v>
       </c>
       <c r="X39" t="n">
-        <v>3573358.88</v>
+        <v>3045130.85</v>
       </c>
       <c r="Y39" t="n">
-        <v>743258.65</v>
+        <v>797824.28</v>
       </c>
       <c r="Z39" t="n">
-        <v>2830100.24</v>
+        <v>2247306.57</v>
       </c>
       <c r="AA39" t="n">
-        <v>2144015.33</v>
+        <v>1827078.51</v>
       </c>
       <c r="AB39" t="n">
-        <v>686084.91</v>
+        <v>420228.06</v>
       </c>
       <c r="AC39" t="n">
-        <v>34721214.37</v>
+        <v>20552657.14</v>
       </c>
       <c r="AD39" t="n">
-        <v>4920805.71</v>
+        <v>5323271.78</v>
       </c>
       <c r="AE39" t="n">
-        <v>29800408.66</v>
+        <v>15229385.36</v>
       </c>
     </row>
     <row r="40">
@@ -4218,86 +4208,86 @@
         <v>3</v>
       </c>
       <c r="D40" t="n">
-        <v>-2944358.11</v>
+        <v>-2517515.41</v>
       </c>
       <c r="E40" t="n">
-        <v>-346395.07</v>
+        <v>-296178.28</v>
       </c>
       <c r="F40" t="n">
-        <v>-173197.54</v>
+        <v>-148089.14</v>
       </c>
       <c r="G40" t="n">
-        <v>360250.88</v>
+        <v>387993.55</v>
       </c>
       <c r="H40" t="n">
-        <v>270188.16</v>
+        <v>290995.16</v>
       </c>
       <c r="I40" t="n">
-        <v>90062.72</v>
+        <v>96998.39</v>
       </c>
       <c r="J40" t="n">
-        <v>865987.6800000001</v>
+        <v>740445.71</v>
       </c>
       <c r="K40" t="n">
-        <v>692790.14</v>
+        <v>592356.5699999999</v>
       </c>
       <c r="L40" t="n">
-        <v>519592.61</v>
+        <v>444267.42</v>
       </c>
       <c r="M40" t="n">
-        <v>26465779.64</v>
+        <v>12432609.7</v>
       </c>
       <c r="N40" t="n">
-        <v>4966334.47</v>
+        <v>4712988.48</v>
       </c>
       <c r="O40" t="n">
-        <v>69279.00999999999</v>
+        <v>59235.66</v>
       </c>
       <c r="P40" t="n">
-        <v>6636743.61</v>
+        <v>3650794.52</v>
       </c>
       <c r="Q40" t="n">
-        <v>-1272949.18</v>
+        <v>-688940.26</v>
       </c>
       <c r="R40" t="n">
-        <v>-1521988.16</v>
+        <v>-1257958.12</v>
       </c>
       <c r="S40" t="n">
-        <v>-103918.52</v>
+        <v>-88853.48</v>
       </c>
       <c r="T40" t="n">
-        <v>-4773793.67</v>
+        <v>-3181765.12</v>
       </c>
       <c r="U40" t="inlineStr"/>
       <c r="V40" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W40" t="n">
-        <v>-28409494.76</v>
+        <v>-14507134.15</v>
       </c>
       <c r="X40" t="n">
-        <v>3463950.72</v>
+        <v>2961782.83</v>
       </c>
       <c r="Y40" t="n">
-        <v>720501.75</v>
+        <v>775987.1</v>
       </c>
       <c r="Z40" t="n">
-        <v>2743448.97</v>
+        <v>2185795.73</v>
       </c>
       <c r="AA40" t="n">
-        <v>2078370.43</v>
+        <v>1777069.7</v>
       </c>
       <c r="AB40" t="n">
-        <v>665078.54</v>
+        <v>408726.03</v>
       </c>
       <c r="AC40" t="n">
-        <v>36865187.55</v>
+        <v>20166688.1</v>
       </c>
       <c r="AD40" t="n">
-        <v>6399700.35</v>
+        <v>4528576.72</v>
       </c>
       <c r="AE40" t="n">
-        <v>30465487.2</v>
+        <v>15638111.39</v>
       </c>
     </row>
     <row r="41">
@@ -4313,86 +4303,86 @@
         <v>4</v>
       </c>
       <c r="D41" t="n">
-        <v>-3290013.79</v>
+        <v>-2790492.8</v>
       </c>
       <c r="E41" t="n">
-        <v>-387060.45</v>
+        <v>-328293.27</v>
       </c>
       <c r="F41" t="n">
-        <v>-193530.22</v>
+        <v>-164146.64</v>
       </c>
       <c r="G41" t="n">
-        <v>402542.86</v>
+        <v>430064.18</v>
       </c>
       <c r="H41" t="n">
-        <v>301907.15</v>
+        <v>322548.14</v>
       </c>
       <c r="I41" t="n">
-        <v>100635.72</v>
+        <v>107516.05</v>
       </c>
       <c r="J41" t="n">
-        <v>967651.11</v>
+        <v>820733.1800000001</v>
       </c>
       <c r="K41" t="n">
-        <v>774120.89</v>
+        <v>656586.54</v>
       </c>
       <c r="L41" t="n">
-        <v>580590.67</v>
+        <v>492439.91</v>
       </c>
       <c r="M41" t="n">
-        <v>24977667.29</v>
+        <v>11979962.65</v>
       </c>
       <c r="N41" t="n">
-        <v>5592918.36</v>
+        <v>5285973.1</v>
       </c>
       <c r="O41" t="n">
-        <v>77412.09</v>
+        <v>65658.64999999999</v>
       </c>
       <c r="P41" t="n">
-        <v>6649079.57</v>
+        <v>3657580.39</v>
       </c>
       <c r="Q41" t="n">
-        <v>-1308015.65</v>
+        <v>-707918.78</v>
       </c>
       <c r="R41" t="n">
-        <v>-1291939.84</v>
+        <v>-1260806.7</v>
       </c>
       <c r="S41" t="n">
-        <v>-116118.13</v>
+        <v>-98487.98</v>
       </c>
       <c r="T41" t="n">
-        <v>-3372360.41</v>
+        <v>-2830805.22</v>
       </c>
       <c r="U41" t="inlineStr"/>
       <c r="V41" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W41" t="n">
-        <v>-29152650.81</v>
+        <v>-14960178.86</v>
       </c>
       <c r="X41" t="n">
-        <v>3870604.45</v>
+        <v>3282932.7</v>
       </c>
       <c r="Y41" t="n">
-        <v>805085.73</v>
+        <v>860128.37</v>
       </c>
       <c r="Z41" t="n">
-        <v>3065518.73</v>
+        <v>2422804.33</v>
       </c>
       <c r="AA41" t="n">
-        <v>2322362.67</v>
+        <v>1969759.62</v>
       </c>
       <c r="AB41" t="n">
-        <v>743156.0600000001</v>
+        <v>453044.71</v>
       </c>
       <c r="AC41" t="n">
-        <v>35989061.64</v>
+        <v>20281256.01</v>
       </c>
       <c r="AD41" t="n">
-        <v>4780418.39</v>
+        <v>4190099.91</v>
       </c>
       <c r="AE41" t="n">
-        <v>31208643.26</v>
+        <v>16091156.1</v>
       </c>
     </row>
     <row r="42">
@@ -4408,86 +4398,86 @@
         <v>5</v>
       </c>
       <c r="D42" t="n">
-        <v>-3066631.89</v>
+        <v>-2969074.23</v>
       </c>
       <c r="E42" t="n">
-        <v>-360780.22</v>
+        <v>-349302.85</v>
       </c>
       <c r="F42" t="n">
-        <v>-180390.11</v>
+        <v>-174651.43</v>
       </c>
       <c r="G42" t="n">
-        <v>375211.43</v>
+        <v>457586.73</v>
       </c>
       <c r="H42" t="n">
-        <v>281408.57</v>
+        <v>343190.05</v>
       </c>
       <c r="I42" t="n">
-        <v>93802.86</v>
+        <v>114396.68</v>
       </c>
       <c r="J42" t="n">
-        <v>901950.5600000001</v>
+        <v>873257.13</v>
       </c>
       <c r="K42" t="n">
-        <v>721560.45</v>
+        <v>698605.7</v>
       </c>
       <c r="L42" t="n">
-        <v>541170.33</v>
+        <v>523954.28</v>
       </c>
       <c r="M42" t="n">
-        <v>27237846.83</v>
+        <v>14387519.42</v>
       </c>
       <c r="N42" t="n">
-        <v>5861500.95</v>
+        <v>5725491.48</v>
       </c>
       <c r="O42" t="n">
-        <v>72156.03999999999</v>
+        <v>69860.57000000001</v>
       </c>
       <c r="P42" t="n">
-        <v>6661415.52</v>
+        <v>3664366.25</v>
       </c>
       <c r="Q42" t="n">
-        <v>-1343203.46</v>
+        <v>-726962.98</v>
       </c>
       <c r="R42" t="n">
-        <v>-1251705.96</v>
+        <v>-1622517.27</v>
       </c>
       <c r="S42" t="n">
-        <v>-108234.07</v>
+        <v>-104790.86</v>
       </c>
       <c r="T42" t="n">
-        <v>-5228434.58</v>
+        <v>-4819772.58</v>
       </c>
       <c r="U42" t="inlineStr"/>
       <c r="V42" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W42" t="n">
-        <v>-29845348.84</v>
+        <v>-15442216.8</v>
       </c>
       <c r="X42" t="n">
-        <v>3607802.23</v>
+        <v>3493028.51</v>
       </c>
       <c r="Y42" t="n">
-        <v>750422.86</v>
+        <v>915173.47</v>
       </c>
       <c r="Z42" t="n">
-        <v>2857379.37</v>
+        <v>2577855.04</v>
       </c>
       <c r="AA42" t="n">
-        <v>2164681.34</v>
+        <v>2095817.11</v>
       </c>
       <c r="AB42" t="n">
-        <v>692698.03</v>
+        <v>482037.93</v>
       </c>
       <c r="AC42" t="n">
-        <v>38489715.89</v>
+        <v>23120274.74</v>
       </c>
       <c r="AD42" t="n">
-        <v>6588374.61</v>
+        <v>6547080.71</v>
       </c>
       <c r="AE42" t="n">
-        <v>31901341.29</v>
+        <v>16573194.03</v>
       </c>
     </row>
     <row r="43">
@@ -4503,86 +4493,86 @@
         <v>6</v>
       </c>
       <c r="D43" t="n">
-        <v>-3355485.16</v>
+        <v>-3129611.16</v>
       </c>
       <c r="E43" t="n">
-        <v>-394762.96</v>
+        <v>-368189.55</v>
       </c>
       <c r="F43" t="n">
-        <v>-197381.48</v>
+        <v>-184094.77</v>
       </c>
       <c r="G43" t="n">
-        <v>410553.48</v>
+        <v>482328.31</v>
       </c>
       <c r="H43" t="n">
-        <v>307915.11</v>
+        <v>361746.23</v>
       </c>
       <c r="I43" t="n">
-        <v>102638.37</v>
+        <v>120582.08</v>
       </c>
       <c r="J43" t="n">
-        <v>986907.4</v>
+        <v>920473.87</v>
       </c>
       <c r="K43" t="n">
-        <v>789525.92</v>
+        <v>736379.1</v>
       </c>
       <c r="L43" t="n">
-        <v>592144.4399999999</v>
+        <v>552284.3199999999</v>
       </c>
       <c r="M43" t="n">
-        <v>26726424.84</v>
+        <v>15439656.84</v>
       </c>
       <c r="N43" t="n">
-        <v>5594317.75</v>
+        <v>6070249.23</v>
       </c>
       <c r="O43" t="n">
-        <v>78952.59</v>
+        <v>73637.91</v>
       </c>
       <c r="P43" t="n">
-        <v>6673751.48</v>
+        <v>3671152.11</v>
       </c>
       <c r="Q43" t="n">
-        <v>-1378512.6</v>
+        <v>-746072.85</v>
       </c>
       <c r="R43" t="n">
-        <v>-1579717.25</v>
+        <v>-1896863.25</v>
       </c>
       <c r="S43" t="n">
-        <v>-118428.89</v>
+        <v>-110456.86</v>
       </c>
       <c r="T43" t="n">
-        <v>-3337501.75</v>
+        <v>-5420007.51</v>
       </c>
       <c r="U43" t="inlineStr"/>
       <c r="V43" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W43" t="n">
-        <v>-30603293.72</v>
+        <v>-15950318.37</v>
       </c>
       <c r="X43" t="n">
-        <v>3947629.6</v>
+        <v>3681895.49</v>
       </c>
       <c r="Y43" t="n">
-        <v>821106.96</v>
+        <v>964656.62</v>
       </c>
       <c r="Z43" t="n">
-        <v>3126522.64</v>
+        <v>2717238.87</v>
       </c>
       <c r="AA43" t="n">
-        <v>2368577.76</v>
+        <v>2209137.29</v>
       </c>
       <c r="AB43" t="n">
-        <v>757944.88</v>
+        <v>508101.58</v>
       </c>
       <c r="AC43" t="n">
-        <v>37694934.05</v>
+        <v>24508623.24</v>
       </c>
       <c r="AD43" t="n">
-        <v>5035647.88</v>
+        <v>7427327.63</v>
       </c>
       <c r="AE43" t="n">
-        <v>32659286.17</v>
+        <v>17081295.61</v>
       </c>
     </row>
     <row r="44">
@@ -4598,86 +4588,86 @@
         <v>7</v>
       </c>
       <c r="D44" t="n">
-        <v>-3438743.27</v>
+        <v>-3196270.04</v>
       </c>
       <c r="E44" t="n">
-        <v>-404558.03</v>
+        <v>-376031.77</v>
       </c>
       <c r="F44" t="n">
-        <v>-202279.02</v>
+        <v>-188015.88</v>
       </c>
       <c r="G44" t="n">
-        <v>420740.35</v>
+        <v>492601.62</v>
       </c>
       <c r="H44" t="n">
-        <v>315555.26</v>
+        <v>369451.21</v>
       </c>
       <c r="I44" t="n">
-        <v>105185.09</v>
+        <v>123150.4</v>
       </c>
       <c r="J44" t="n">
-        <v>1011395.08</v>
+        <v>940079.42</v>
       </c>
       <c r="K44" t="n">
-        <v>809116.0600000001</v>
+        <v>752063.54</v>
       </c>
       <c r="L44" t="n">
-        <v>606837.05</v>
+        <v>564047.65</v>
       </c>
       <c r="M44" t="n">
-        <v>28652319.99</v>
+        <v>15719168.43</v>
       </c>
       <c r="N44" t="n">
-        <v>6112644.43</v>
+        <v>5795938.15</v>
       </c>
       <c r="O44" t="n">
-        <v>80911.61</v>
+        <v>75206.35000000001</v>
       </c>
       <c r="P44" t="n">
-        <v>6686087.43</v>
+        <v>3677937.98</v>
       </c>
       <c r="Q44" t="n">
-        <v>-1413943.08</v>
+        <v>-765248.39</v>
       </c>
       <c r="R44" t="n">
-        <v>-1443985.38</v>
+        <v>-1613104.16</v>
       </c>
       <c r="S44" t="n">
-        <v>-121367.41</v>
+        <v>-112809.53</v>
       </c>
       <c r="T44" t="n">
-        <v>-5116629.99</v>
+        <v>-5176869.39</v>
       </c>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W44" t="n">
-        <v>-31380045.14</v>
+        <v>-16469242.21</v>
       </c>
       <c r="X44" t="n">
-        <v>4045580.32</v>
+        <v>3760317.69</v>
       </c>
       <c r="Y44" t="n">
-        <v>841480.71</v>
+        <v>985203.24</v>
       </c>
       <c r="Z44" t="n">
-        <v>3204099.61</v>
+        <v>2775114.46</v>
       </c>
       <c r="AA44" t="n">
-        <v>2427348.19</v>
+        <v>2256190.62</v>
       </c>
       <c r="AB44" t="n">
-        <v>776751.42</v>
+        <v>518923.84</v>
       </c>
       <c r="AC44" t="n">
-        <v>40118020.37</v>
+        <v>24503002.53</v>
       </c>
       <c r="AD44" t="n">
-        <v>6681982.78</v>
+        <v>6902783.08</v>
       </c>
       <c r="AE44" t="n">
-        <v>33436037.59</v>
+        <v>17600219.45</v>
       </c>
     </row>
     <row r="45">
@@ -4693,86 +4683,86 @@
         <v>8</v>
       </c>
       <c r="D45" t="n">
-        <v>-3526275.65</v>
+        <v>-3196737.99</v>
       </c>
       <c r="E45" t="n">
-        <v>-414855.96</v>
+        <v>-376086.82</v>
       </c>
       <c r="F45" t="n">
-        <v>-207427.98</v>
+        <v>-188043.41</v>
       </c>
       <c r="G45" t="n">
-        <v>431450.2</v>
+        <v>492673.74</v>
       </c>
       <c r="H45" t="n">
-        <v>323587.65</v>
+        <v>369505.3</v>
       </c>
       <c r="I45" t="n">
-        <v>107862.55</v>
+        <v>123168.43</v>
       </c>
       <c r="J45" t="n">
-        <v>1037139.9</v>
+        <v>940217.05</v>
       </c>
       <c r="K45" t="n">
-        <v>829711.92</v>
+        <v>752173.64</v>
       </c>
       <c r="L45" t="n">
-        <v>622283.9399999999</v>
+        <v>564130.23</v>
       </c>
       <c r="M45" t="n">
-        <v>29936474.71</v>
+        <v>16573677.8</v>
       </c>
       <c r="N45" t="n">
-        <v>5768931.89</v>
+        <v>5510374.32</v>
       </c>
       <c r="O45" t="n">
-        <v>82971.19</v>
+        <v>75217.36</v>
       </c>
       <c r="P45" t="n">
-        <v>6698423.38</v>
+        <v>3684723.84</v>
       </c>
       <c r="Q45" t="n">
-        <v>-1449494.9</v>
+        <v>-784489.59</v>
       </c>
       <c r="R45" t="n">
-        <v>-1834030.81</v>
+        <v>-1795473.46</v>
       </c>
       <c r="S45" t="n">
-        <v>-124456.79</v>
+        <v>-112826.05</v>
       </c>
       <c r="T45" t="n">
-        <v>-4846257.65</v>
+        <v>-5031984.95</v>
       </c>
       <c r="U45" t="inlineStr"/>
       <c r="V45" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W45" t="n">
-        <v>-32176568.58</v>
+        <v>-16988242.03</v>
       </c>
       <c r="X45" t="n">
-        <v>4148559.58</v>
+        <v>3760868.22</v>
       </c>
       <c r="Y45" t="n">
-        <v>862900.39</v>
+        <v>985347.47</v>
       </c>
       <c r="Z45" t="n">
-        <v>3285659.19</v>
+        <v>2775520.74</v>
       </c>
       <c r="AA45" t="n">
-        <v>2489135.75</v>
+        <v>2256520.93</v>
       </c>
       <c r="AB45" t="n">
-        <v>796523.4399999999</v>
+        <v>518999.81</v>
       </c>
       <c r="AC45" t="n">
-        <v>41037306.28</v>
+        <v>25059503.73</v>
       </c>
       <c r="AD45" t="n">
-        <v>6804745.25</v>
+        <v>6940284.46</v>
       </c>
       <c r="AE45" t="n">
-        <v>34232561.03</v>
+        <v>18119219.27</v>
       </c>
     </row>
     <row r="46">
@@ -4788,86 +4778,86 @@
         <v>9</v>
       </c>
       <c r="D46" t="n">
-        <v>-3665993.74</v>
+        <v>-3254163.92</v>
       </c>
       <c r="E46" t="n">
-        <v>-431293.38</v>
+        <v>-382842.81</v>
       </c>
       <c r="F46" t="n">
-        <v>-215646.69</v>
+        <v>-191421.41</v>
       </c>
       <c r="G46" t="n">
-        <v>448545.12</v>
+        <v>501524.09</v>
       </c>
       <c r="H46" t="n">
-        <v>336408.84</v>
+        <v>376143.07</v>
       </c>
       <c r="I46" t="n">
-        <v>112136.28</v>
+        <v>125381.02</v>
       </c>
       <c r="J46" t="n">
-        <v>1078233.45</v>
+        <v>957107.04</v>
       </c>
       <c r="K46" t="n">
-        <v>862586.76</v>
+        <v>765685.63</v>
       </c>
       <c r="L46" t="n">
-        <v>646940.0699999999</v>
+        <v>574264.22</v>
       </c>
       <c r="M46" t="n">
-        <v>29182922.99</v>
+        <v>16085771.85</v>
       </c>
       <c r="N46" t="n">
-        <v>6487814.29</v>
+        <v>5730568.51</v>
       </c>
       <c r="O46" t="n">
-        <v>86258.67999999999</v>
+        <v>76568.56</v>
       </c>
       <c r="P46" t="n">
-        <v>6710759.34</v>
+        <v>3691509.7</v>
       </c>
       <c r="Q46" t="n">
-        <v>-1485168.05</v>
+        <v>-803796.47</v>
       </c>
       <c r="R46" t="n">
-        <v>-1865569.6</v>
+        <v>-1734478.45</v>
       </c>
       <c r="S46" t="n">
-        <v>-129388.01</v>
+        <v>-114852.84</v>
       </c>
       <c r="T46" t="n">
-        <v>-3926985.3</v>
+        <v>-4283748.52</v>
       </c>
       <c r="U46" t="inlineStr"/>
       <c r="V46" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W46" t="n">
-        <v>-33004651.88</v>
+        <v>-17516565.11</v>
       </c>
       <c r="X46" t="n">
-        <v>4312933.81</v>
+        <v>3828428.15</v>
       </c>
       <c r="Y46" t="n">
-        <v>897090.23</v>
+        <v>1003048.17</v>
       </c>
       <c r="Z46" t="n">
-        <v>3415843.58</v>
+        <v>2825379.97</v>
       </c>
       <c r="AA46" t="n">
-        <v>2587760.29</v>
+        <v>2297056.89</v>
       </c>
       <c r="AB46" t="n">
-        <v>828083.29</v>
+        <v>528323.08</v>
       </c>
       <c r="AC46" t="n">
-        <v>40982587.24</v>
+        <v>24780622.16</v>
       </c>
       <c r="AD46" t="n">
-        <v>5921942.92</v>
+        <v>6133079.81</v>
       </c>
       <c r="AE46" t="n">
-        <v>35060644.32</v>
+        <v>18647542.35</v>
       </c>
     </row>
     <row r="47">
@@ -4883,86 +4873,86 @@
         <v>10</v>
       </c>
       <c r="D47" t="n">
-        <v>-4113149.76</v>
+        <v>-3633683.06</v>
       </c>
       <c r="E47" t="n">
-        <v>-483899.97</v>
+        <v>-427492.12</v>
       </c>
       <c r="F47" t="n">
-        <v>-241949.99</v>
+        <v>-213746.06</v>
       </c>
       <c r="G47" t="n">
-        <v>503255.97</v>
+        <v>560014.6800000001</v>
       </c>
       <c r="H47" t="n">
-        <v>377441.98</v>
+        <v>420011.01</v>
       </c>
       <c r="I47" t="n">
-        <v>125813.99</v>
+        <v>140003.67</v>
       </c>
       <c r="J47" t="n">
-        <v>1209749.93</v>
+        <v>1068730.31</v>
       </c>
       <c r="K47" t="n">
-        <v>967799.9399999999</v>
+        <v>854984.25</v>
       </c>
       <c r="L47" t="n">
-        <v>725849.96</v>
+        <v>641238.1899999999</v>
       </c>
       <c r="M47" t="n">
-        <v>31700311.04</v>
+        <v>15460125.74</v>
       </c>
       <c r="N47" t="n">
-        <v>8022319.74</v>
+        <v>6669409.83</v>
       </c>
       <c r="O47" t="n">
-        <v>96779.99000000001</v>
+        <v>85498.42</v>
       </c>
       <c r="P47" t="n">
-        <v>6723095.29</v>
+        <v>3698295.57</v>
       </c>
       <c r="Q47" t="n">
-        <v>-1520962.54</v>
+        <v>-823169.01</v>
       </c>
       <c r="R47" t="n">
-        <v>-1672510.26</v>
+        <v>-1686688.94</v>
       </c>
       <c r="S47" t="n">
-        <v>-145169.99</v>
+        <v>-128247.64</v>
       </c>
       <c r="T47" t="n">
-        <v>-7214131.01</v>
+        <v>-4037742.48</v>
       </c>
       <c r="U47" t="inlineStr"/>
       <c r="V47" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W47" t="n">
-        <v>-33933739.82</v>
+        <v>-18106504.25</v>
       </c>
       <c r="X47" t="n">
-        <v>4838999.72</v>
+        <v>4274921.25</v>
       </c>
       <c r="Y47" t="n">
-        <v>1006511.94</v>
+        <v>1120029.37</v>
       </c>
       <c r="Z47" t="n">
-        <v>3832487.78</v>
+        <v>3154891.88</v>
       </c>
       <c r="AA47" t="n">
-        <v>2903399.83</v>
+        <v>2564952.75</v>
       </c>
       <c r="AB47" t="n">
-        <v>929087.95</v>
+        <v>589939.13</v>
       </c>
       <c r="AC47" t="n">
-        <v>45021543.52</v>
+        <v>25090160.55</v>
       </c>
       <c r="AD47" t="n">
-        <v>9031811.26</v>
+        <v>5852679.07</v>
       </c>
       <c r="AE47" t="n">
-        <v>35989732.27</v>
+        <v>19237481.48</v>
       </c>
     </row>
     <row r="48">
@@ -4978,86 +4968,86 @@
         <v>11</v>
       </c>
       <c r="D48" t="n">
-        <v>-4399959.94</v>
+        <v>-3825099.65</v>
       </c>
       <c r="E48" t="n">
-        <v>-517642.35</v>
+        <v>-450011.72</v>
       </c>
       <c r="F48" t="n">
-        <v>-258821.17</v>
+        <v>-225005.86</v>
       </c>
       <c r="G48" t="n">
-        <v>538348.04</v>
+        <v>589515.36</v>
       </c>
       <c r="H48" t="n">
-        <v>403761.03</v>
+        <v>442136.52</v>
       </c>
       <c r="I48" t="n">
-        <v>134587.01</v>
+        <v>147378.84</v>
       </c>
       <c r="J48" t="n">
-        <v>1294105.86</v>
+        <v>1125029.31</v>
       </c>
       <c r="K48" t="n">
-        <v>1035284.69</v>
+        <v>900023.45</v>
       </c>
       <c r="L48" t="n">
-        <v>776463.52</v>
+        <v>675017.59</v>
       </c>
       <c r="M48" t="n">
-        <v>32971171.2</v>
+        <v>18306594.7</v>
       </c>
       <c r="N48" t="n">
-        <v>7037724.63</v>
+        <v>6074785.66</v>
       </c>
       <c r="O48" t="n">
-        <v>103528.47</v>
+        <v>90002.34</v>
       </c>
       <c r="P48" t="n">
-        <v>6735431.25</v>
+        <v>3705081.43</v>
       </c>
       <c r="Q48" t="n">
-        <v>-1556878.37</v>
+        <v>-842607.23</v>
       </c>
       <c r="R48" t="n">
-        <v>-2290479.7</v>
+        <v>-1715226.22</v>
       </c>
       <c r="S48" t="n">
-        <v>-155292.7</v>
+        <v>-135003.52</v>
       </c>
       <c r="T48" t="n">
-        <v>-5861599.21</v>
+        <v>-5625129.51</v>
       </c>
       <c r="U48" t="inlineStr"/>
       <c r="V48" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W48" t="n">
-        <v>-34927613.12</v>
+        <v>-18727520.42</v>
       </c>
       <c r="X48" t="n">
-        <v>5176423.45</v>
+        <v>4500117.24</v>
       </c>
       <c r="Y48" t="n">
-        <v>1076696.08</v>
+        <v>1179030.72</v>
       </c>
       <c r="Z48" t="n">
-        <v>4099727.38</v>
+        <v>3321086.52</v>
       </c>
       <c r="AA48" t="n">
-        <v>3105854.07</v>
+        <v>2700070.34</v>
       </c>
       <c r="AB48" t="n">
-        <v>993873.3</v>
+        <v>621016.1800000001</v>
       </c>
       <c r="AC48" t="n">
-        <v>45290977.18</v>
+        <v>27333856.91</v>
       </c>
       <c r="AD48" t="n">
-        <v>8307371.61</v>
+        <v>7475359.25</v>
       </c>
       <c r="AE48" t="n">
-        <v>36983605.57</v>
+        <v>19858497.66</v>
       </c>
     </row>
     <row r="49">
@@ -5073,86 +5063,86 @@
         <v>12</v>
       </c>
       <c r="D49" t="n">
-        <v>-4701606.46</v>
+        <v>-4036236.93</v>
       </c>
       <c r="E49" t="n">
-        <v>-553130.17</v>
+        <v>-474851.4</v>
       </c>
       <c r="F49" t="n">
-        <v>-276565.09</v>
+        <v>-237425.7</v>
       </c>
       <c r="G49" t="n">
-        <v>575255.38</v>
+        <v>622055.34</v>
       </c>
       <c r="H49" t="n">
-        <v>431441.53</v>
+        <v>466541.5</v>
       </c>
       <c r="I49" t="n">
-        <v>143813.84</v>
+        <v>155513.83</v>
       </c>
       <c r="J49" t="n">
-        <v>1382825.43</v>
+        <v>1187128.51</v>
       </c>
       <c r="K49" t="n">
-        <v>1106260.34</v>
+        <v>949702.8100000001</v>
       </c>
       <c r="L49" t="n">
-        <v>829695.26</v>
+        <v>712277.11</v>
       </c>
       <c r="M49" t="n">
-        <v>31034709.67</v>
+        <v>18968114.18</v>
       </c>
       <c r="N49" t="n">
-        <v>9136272.58</v>
+        <v>7000183.33</v>
       </c>
       <c r="O49" t="n">
-        <v>110626.03</v>
+        <v>94970.28</v>
       </c>
       <c r="P49" t="n">
-        <v>6747767.2</v>
+        <v>3711867.29</v>
       </c>
       <c r="Q49" t="n">
-        <v>-1592915.54</v>
+        <v>-862111.11</v>
       </c>
       <c r="R49" t="n">
-        <v>-1792108.45</v>
+        <v>-2427345.02</v>
       </c>
       <c r="S49" t="n">
-        <v>-165939.05</v>
+        <v>-142455.42</v>
       </c>
       <c r="T49" t="n">
-        <v>-5432796.96</v>
+        <v>-5829430.93</v>
       </c>
       <c r="U49" t="inlineStr"/>
       <c r="V49" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W49" t="n">
-        <v>-35989623.05</v>
+        <v>-19382815.36</v>
       </c>
       <c r="X49" t="n">
-        <v>5531301.72</v>
+        <v>4748514.04</v>
       </c>
       <c r="Y49" t="n">
-        <v>1150510.76</v>
+        <v>1244110.68</v>
       </c>
       <c r="Z49" t="n">
-        <v>4380790.96</v>
+        <v>3504403.36</v>
       </c>
       <c r="AA49" t="n">
-        <v>3318781.03</v>
+        <v>2849108.42</v>
       </c>
       <c r="AB49" t="n">
-        <v>1062009.93</v>
+        <v>655294.9399999999</v>
       </c>
       <c r="AC49" t="n">
-        <v>45436459.96</v>
+        <v>28913023.97</v>
       </c>
       <c r="AD49" t="n">
-        <v>7390844.46</v>
+        <v>8399231.369999999</v>
       </c>
       <c r="AE49" t="n">
-        <v>38045615.5</v>
+        <v>20513792.6</v>
       </c>
     </row>
     <row r="50">
@@ -5168,86 +5158,86 @@
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>-3636276.29</v>
+        <v>-3226924.07</v>
       </c>
       <c r="E50" t="n">
-        <v>-427797.21</v>
+        <v>-379638.13</v>
       </c>
       <c r="F50" t="n">
-        <v>-213898.61</v>
+        <v>-189819.06</v>
       </c>
       <c r="G50" t="n">
-        <v>444909.1</v>
+        <v>497325.95</v>
       </c>
       <c r="H50" t="n">
-        <v>333681.82</v>
+        <v>372994.46</v>
       </c>
       <c r="I50" t="n">
-        <v>111227.27</v>
+        <v>124331.49</v>
       </c>
       <c r="J50" t="n">
-        <v>1069493.03</v>
+        <v>949095.3199999999</v>
       </c>
       <c r="K50" t="n">
-        <v>855594.42</v>
+        <v>759276.25</v>
       </c>
       <c r="L50" t="n">
-        <v>641695.8199999999</v>
+        <v>569457.1899999999</v>
       </c>
       <c r="M50" t="n">
-        <v>31690875.81</v>
+        <v>19752392.7</v>
       </c>
       <c r="N50" t="n">
-        <v>6958989.16</v>
+        <v>5685162.95</v>
       </c>
       <c r="O50" t="n">
-        <v>85559.44</v>
+        <v>75927.63</v>
       </c>
       <c r="P50" t="n">
-        <v>6760103.16</v>
+        <v>3718653.16</v>
       </c>
       <c r="Q50" t="n">
-        <v>-1629074.04</v>
+        <v>-881680.67</v>
       </c>
       <c r="R50" t="n">
-        <v>-1426213.73</v>
+        <v>-1516371.32</v>
       </c>
       <c r="S50" t="n">
-        <v>-128339.16</v>
+        <v>-113891.44</v>
       </c>
       <c r="T50" t="n">
-        <v>-3444914.5</v>
+        <v>-5682499.8</v>
       </c>
       <c r="U50" t="inlineStr"/>
       <c r="V50" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W50" t="n">
-        <v>-36810993.7</v>
+        <v>-19906715.98</v>
       </c>
       <c r="X50" t="n">
-        <v>4277972.11</v>
+        <v>3796381.26</v>
       </c>
       <c r="Y50" t="n">
-        <v>889818.2</v>
+        <v>994651.89</v>
       </c>
       <c r="Z50" t="n">
-        <v>3388153.91</v>
+        <v>2801729.37</v>
       </c>
       <c r="AA50" t="n">
-        <v>2566783.27</v>
+        <v>2277828.76</v>
       </c>
       <c r="AB50" t="n">
-        <v>821370.65</v>
+        <v>523900.61</v>
       </c>
       <c r="AC50" t="n">
-        <v>43866453.53</v>
+        <v>28350455.77</v>
       </c>
       <c r="AD50" t="n">
-        <v>4999467.39</v>
+        <v>7312762.56</v>
       </c>
       <c r="AE50" t="n">
-        <v>38866986.14</v>
+        <v>21037693.21</v>
       </c>
     </row>
     <row r="51">
@@ -5263,86 +5253,86 @@
         <v>2</v>
       </c>
       <c r="D51" t="n">
-        <v>-3646596.66</v>
+        <v>-3304721.72</v>
       </c>
       <c r="E51" t="n">
-        <v>-429011.37</v>
+        <v>-388790.79</v>
       </c>
       <c r="F51" t="n">
-        <v>-214505.69</v>
+        <v>-194395.4</v>
       </c>
       <c r="G51" t="n">
-        <v>446171.83</v>
+        <v>509315.94</v>
       </c>
       <c r="H51" t="n">
-        <v>334628.87</v>
+        <v>381986.95</v>
       </c>
       <c r="I51" t="n">
-        <v>111542.96</v>
+        <v>127328.98</v>
       </c>
       <c r="J51" t="n">
-        <v>1072528.43</v>
+        <v>971976.98</v>
       </c>
       <c r="K51" t="n">
-        <v>858022.74</v>
+        <v>777581.58</v>
       </c>
       <c r="L51" t="n">
-        <v>643517.0600000001</v>
+        <v>583186.1899999999</v>
       </c>
       <c r="M51" t="n">
-        <v>33517738.27</v>
+        <v>19141319.16</v>
       </c>
       <c r="N51" t="n">
-        <v>6855992.4</v>
+        <v>5977788.63</v>
       </c>
       <c r="O51" t="n">
-        <v>85802.27</v>
+        <v>77758.16</v>
       </c>
       <c r="P51" t="n">
-        <v>6772439.11</v>
+        <v>3725439.02</v>
       </c>
       <c r="Q51" t="n">
-        <v>-1665353.88</v>
+        <v>-901315.89</v>
       </c>
       <c r="R51" t="n">
-        <v>-1663946.59</v>
+        <v>-1498472.84</v>
       </c>
       <c r="S51" t="n">
-        <v>-128703.41</v>
+        <v>-116637.24</v>
       </c>
       <c r="T51" t="n">
-        <v>-4083280.19</v>
+        <v>-4831654.5</v>
       </c>
       <c r="U51" t="inlineStr"/>
       <c r="V51" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W51" t="n">
-        <v>-37634695.53</v>
+        <v>-20443247.27</v>
       </c>
       <c r="X51" t="n">
-        <v>4290113.72</v>
+        <v>3887907.9</v>
       </c>
       <c r="Y51" t="n">
-        <v>892343.65</v>
+        <v>1018631.87</v>
       </c>
       <c r="Z51" t="n">
-        <v>3397770.07</v>
+        <v>2869276.03</v>
       </c>
       <c r="AA51" t="n">
-        <v>2574068.23</v>
+        <v>2332744.74</v>
       </c>
       <c r="AB51" t="n">
-        <v>823701.83</v>
+        <v>536531.29</v>
       </c>
       <c r="AC51" t="n">
-        <v>45566618.17</v>
+        <v>28020989.08</v>
       </c>
       <c r="AD51" t="n">
-        <v>5875930.19</v>
+        <v>6446764.57</v>
       </c>
       <c r="AE51" t="n">
-        <v>39690687.98</v>
+        <v>21574224.5</v>
       </c>
     </row>
     <row r="52">
@@ -5358,86 +5348,86 @@
         <v>3</v>
       </c>
       <c r="D52" t="n">
-        <v>-3776265.01</v>
+        <v>-3166576.69</v>
       </c>
       <c r="E52" t="n">
-        <v>-444266.47</v>
+        <v>-372538.43</v>
       </c>
       <c r="F52" t="n">
-        <v>-222133.24</v>
+        <v>-186269.22</v>
       </c>
       <c r="G52" t="n">
-        <v>462037.13</v>
+        <v>488025.35</v>
       </c>
       <c r="H52" t="n">
-        <v>346527.85</v>
+        <v>366019.01</v>
       </c>
       <c r="I52" t="n">
-        <v>115509.28</v>
+        <v>122006.34</v>
       </c>
       <c r="J52" t="n">
-        <v>1110666.18</v>
+        <v>931346.09</v>
       </c>
       <c r="K52" t="n">
-        <v>888532.9399999999</v>
+        <v>745076.87</v>
       </c>
       <c r="L52" t="n">
-        <v>666399.71</v>
+        <v>558807.65</v>
       </c>
       <c r="M52" t="n">
-        <v>36714622.77</v>
+        <v>19416763.73</v>
       </c>
       <c r="N52" t="n">
-        <v>6573647.74</v>
+        <v>5060251.09</v>
       </c>
       <c r="O52" t="n">
-        <v>88853.28999999999</v>
+        <v>74507.69</v>
       </c>
       <c r="P52" t="n">
-        <v>6784775.07</v>
+        <v>3732224.88</v>
       </c>
       <c r="Q52" t="n">
-        <v>-1701755.06</v>
+        <v>-921016.79</v>
       </c>
       <c r="R52" t="n">
-        <v>-2010767.74</v>
+        <v>-1548911.55</v>
       </c>
       <c r="S52" t="n">
-        <v>-133279.94</v>
+        <v>-111761.53</v>
       </c>
       <c r="T52" t="n">
-        <v>-5772416.52</v>
+        <v>-3613729.98</v>
       </c>
       <c r="U52" t="inlineStr"/>
       <c r="V52" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W52" t="n">
-        <v>-38487687.16</v>
+        <v>-20957350.31</v>
       </c>
       <c r="X52" t="n">
-        <v>4442664.72</v>
+        <v>3725384.34</v>
       </c>
       <c r="Y52" t="n">
-        <v>924074.26</v>
+        <v>976050.7</v>
       </c>
       <c r="Z52" t="n">
-        <v>3518590.46</v>
+        <v>2749333.64</v>
       </c>
       <c r="AA52" t="n">
-        <v>2665598.83</v>
+        <v>2235230.6</v>
       </c>
       <c r="AB52" t="n">
-        <v>852991.63</v>
+        <v>514103.04</v>
       </c>
       <c r="AC52" t="n">
-        <v>48460143.81</v>
+        <v>27362730.61</v>
       </c>
       <c r="AD52" t="n">
-        <v>7916464.2</v>
+        <v>5274403.06</v>
       </c>
       <c r="AE52" t="n">
-        <v>40543679.61</v>
+        <v>22088327.54</v>
       </c>
     </row>
     <row r="53">
@@ -5453,86 +5443,86 @@
         <v>4</v>
       </c>
       <c r="D53" t="n">
-        <v>-3845128.22</v>
+        <v>-3507535.55</v>
       </c>
       <c r="E53" t="n">
-        <v>-452368.03</v>
+        <v>-412651.24</v>
       </c>
       <c r="F53" t="n">
-        <v>-226184.01</v>
+        <v>-206325.62</v>
       </c>
       <c r="G53" t="n">
-        <v>470462.75</v>
+        <v>540573.13</v>
       </c>
       <c r="H53" t="n">
-        <v>352847.06</v>
+        <v>405429.84</v>
       </c>
       <c r="I53" t="n">
-        <v>117615.69</v>
+        <v>135143.28</v>
       </c>
       <c r="J53" t="n">
-        <v>1130920.07</v>
+        <v>1031628.1</v>
       </c>
       <c r="K53" t="n">
-        <v>904736.05</v>
+        <v>825302.48</v>
       </c>
       <c r="L53" t="n">
-        <v>678552.04</v>
+        <v>618976.86</v>
       </c>
       <c r="M53" t="n">
-        <v>38466514.67</v>
+        <v>20237922.78</v>
       </c>
       <c r="N53" t="n">
-        <v>6123520.78</v>
+        <v>6194486.32</v>
       </c>
       <c r="O53" t="n">
-        <v>90473.61</v>
+        <v>82530.25</v>
       </c>
       <c r="P53" t="n">
-        <v>6797111.02</v>
+        <v>3739010.75</v>
       </c>
       <c r="Q53" t="n">
-        <v>-1738277.57</v>
+        <v>-940783.35</v>
       </c>
       <c r="R53" t="n">
-        <v>-1858035.34</v>
+        <v>-2063206.74</v>
       </c>
       <c r="S53" t="n">
-        <v>-135710.41</v>
+        <v>-123795.37</v>
       </c>
       <c r="T53" t="n">
-        <v>-6333370.53</v>
+        <v>-4468378.38</v>
       </c>
       <c r="U53" t="inlineStr"/>
       <c r="V53" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W53" t="n">
-        <v>-39356233.77</v>
+        <v>-21526809.02</v>
       </c>
       <c r="X53" t="n">
-        <v>4523680.26</v>
+        <v>4126512.41</v>
       </c>
       <c r="Y53" t="n">
-        <v>940925.49</v>
+        <v>1081146.25</v>
       </c>
       <c r="Z53" t="n">
-        <v>3582754.77</v>
+        <v>3045366.16</v>
       </c>
       <c r="AA53" t="n">
-        <v>2714208.16</v>
+        <v>2475907.45</v>
       </c>
       <c r="AB53" t="n">
-        <v>868546.61</v>
+        <v>569458.71</v>
       </c>
       <c r="AC53" t="n">
-        <v>49739342.5</v>
+        <v>29313166.74</v>
       </c>
       <c r="AD53" t="n">
-        <v>8327116.28</v>
+        <v>6655380.49</v>
       </c>
       <c r="AE53" t="n">
-        <v>41412226.22</v>
+        <v>22657786.26</v>
       </c>
     </row>
     <row r="54">
@@ -5548,86 +5538,86 @@
         <v>5</v>
       </c>
       <c r="D54" t="n">
-        <v>-4117358.22</v>
+        <v>-3718588.92</v>
       </c>
       <c r="E54" t="n">
-        <v>-484395.08</v>
+        <v>-437481.05</v>
       </c>
       <c r="F54" t="n">
-        <v>-242197.54</v>
+        <v>-218740.52</v>
       </c>
       <c r="G54" t="n">
-        <v>503770.89</v>
+        <v>573100.17</v>
       </c>
       <c r="H54" t="n">
-        <v>377828.17</v>
+        <v>429825.13</v>
       </c>
       <c r="I54" t="n">
-        <v>125942.72</v>
+        <v>143275.04</v>
       </c>
       <c r="J54" t="n">
-        <v>1210987.71</v>
+        <v>1093702.62</v>
       </c>
       <c r="K54" t="n">
-        <v>968790.17</v>
+        <v>874962.1</v>
       </c>
       <c r="L54" t="n">
-        <v>726592.63</v>
+        <v>656221.5699999999</v>
       </c>
       <c r="M54" t="n">
-        <v>37914752.85</v>
+        <v>21117556.81</v>
       </c>
       <c r="N54" t="n">
-        <v>7962418.31</v>
+        <v>6329971.19</v>
       </c>
       <c r="O54" t="n">
-        <v>96879.02</v>
+        <v>87496.21000000001</v>
       </c>
       <c r="P54" t="n">
-        <v>6809446.98</v>
+        <v>3745796.61</v>
       </c>
       <c r="Q54" t="n">
-        <v>-1774921.43</v>
+        <v>-960615.58</v>
       </c>
       <c r="R54" t="n">
-        <v>-1786843.62</v>
+        <v>-1690817.65</v>
       </c>
       <c r="S54" t="n">
-        <v>-145318.53</v>
+        <v>-131244.31</v>
       </c>
       <c r="T54" t="n">
-        <v>-6734148.81</v>
+        <v>-5236633.17</v>
       </c>
       <c r="U54" t="inlineStr"/>
       <c r="V54" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W54" t="n">
-        <v>-40286272.33</v>
+        <v>-22130532.87</v>
       </c>
       <c r="X54" t="n">
-        <v>4843950.85</v>
+        <v>4374810.49</v>
       </c>
       <c r="Y54" t="n">
-        <v>1007541.78</v>
+        <v>1146200.35</v>
       </c>
       <c r="Z54" t="n">
-        <v>3836409.07</v>
+        <v>3228610.14</v>
       </c>
       <c r="AA54" t="n">
-        <v>2906370.51</v>
+        <v>2624886.29</v>
       </c>
       <c r="AB54" t="n">
-        <v>930038.5600000001</v>
+        <v>603723.85</v>
       </c>
       <c r="AC54" t="n">
-        <v>51008575.73</v>
+        <v>30320205.24</v>
       </c>
       <c r="AD54" t="n">
-        <v>8666310.949999999</v>
+        <v>7058695.14</v>
       </c>
       <c r="AE54" t="n">
-        <v>42342264.78</v>
+        <v>23261510.1</v>
       </c>
     </row>
     <row r="55">
@@ -5643,86 +5633,86 @@
         <v>6</v>
       </c>
       <c r="D55" t="n">
-        <v>-4134997.08</v>
+        <v>-3570734.34</v>
       </c>
       <c r="E55" t="n">
-        <v>-486470.25</v>
+        <v>-420086.39</v>
       </c>
       <c r="F55" t="n">
-        <v>-243235.12</v>
+        <v>-210043.2</v>
       </c>
       <c r="G55" t="n">
-        <v>505929.05</v>
+        <v>550313.17</v>
       </c>
       <c r="H55" t="n">
-        <v>379446.79</v>
+        <v>412734.88</v>
       </c>
       <c r="I55" t="n">
-        <v>126482.26</v>
+        <v>137578.29</v>
       </c>
       <c r="J55" t="n">
-        <v>1216175.61</v>
+        <v>1050215.98</v>
       </c>
       <c r="K55" t="n">
-        <v>972940.49</v>
+        <v>840172.79</v>
       </c>
       <c r="L55" t="n">
-        <v>729705.37</v>
+        <v>630129.59</v>
       </c>
       <c r="M55" t="n">
-        <v>39668756.59</v>
+        <v>22752044.63</v>
       </c>
       <c r="N55" t="n">
-        <v>6865554.27</v>
+        <v>5784330.87</v>
       </c>
       <c r="O55" t="n">
-        <v>97294.05</v>
+        <v>84017.28</v>
       </c>
       <c r="P55" t="n">
-        <v>6821782.93</v>
+        <v>3752582.47</v>
       </c>
       <c r="Q55" t="n">
-        <v>-1811686.61</v>
+        <v>-980513.49</v>
       </c>
       <c r="R55" t="n">
-        <v>-2143177.33</v>
+        <v>-1611467.43</v>
       </c>
       <c r="S55" t="n">
-        <v>-145941.07</v>
+        <v>-126025.92</v>
       </c>
       <c r="T55" t="n">
-        <v>-6076295.18</v>
+        <v>-5813739.1</v>
       </c>
       <c r="U55" t="inlineStr"/>
       <c r="V55" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W55" t="n">
-        <v>-41220295.21</v>
+        <v>-22710252.09</v>
       </c>
       <c r="X55" t="n">
-        <v>4864702.45</v>
+        <v>4200863.93</v>
       </c>
       <c r="Y55" t="n">
-        <v>1011858.11</v>
+        <v>1100626.35</v>
       </c>
       <c r="Z55" t="n">
-        <v>3852844.34</v>
+        <v>3100237.58</v>
       </c>
       <c r="AA55" t="n">
-        <v>2918821.47</v>
+        <v>2520518.36</v>
       </c>
       <c r="AB55" t="n">
-        <v>934022.87</v>
+        <v>579719.22</v>
       </c>
       <c r="AC55" t="n">
-        <v>51641701.23</v>
+        <v>31392461.78</v>
       </c>
       <c r="AD55" t="n">
-        <v>8365413.58</v>
+        <v>7551232.45</v>
       </c>
       <c r="AE55" t="n">
-        <v>43276287.65</v>
+        <v>23841229.32</v>
       </c>
     </row>
     <row r="56">
@@ -5738,86 +5728,86 @@
         <v>7</v>
       </c>
       <c r="D56" t="n">
-        <v>-4280530.22</v>
+        <v>-3681917.21</v>
       </c>
       <c r="E56" t="n">
-        <v>-503591.79</v>
+        <v>-433166.73</v>
       </c>
       <c r="F56" t="n">
-        <v>-251795.9</v>
+        <v>-216583.37</v>
       </c>
       <c r="G56" t="n">
-        <v>523735.46</v>
+        <v>567448.42</v>
       </c>
       <c r="H56" t="n">
-        <v>392801.6</v>
+        <v>425586.31</v>
       </c>
       <c r="I56" t="n">
-        <v>130933.87</v>
+        <v>141862.1</v>
       </c>
       <c r="J56" t="n">
-        <v>1258979.48</v>
+        <v>1082916.83</v>
       </c>
       <c r="K56" t="n">
-        <v>1007183.58</v>
+        <v>866333.46</v>
       </c>
       <c r="L56" t="n">
-        <v>755387.6899999999</v>
+        <v>649750.1</v>
       </c>
       <c r="M56" t="n">
-        <v>40090372.82</v>
+        <v>22535428.95</v>
       </c>
       <c r="N56" t="n">
-        <v>6916172.37</v>
+        <v>6570844.94</v>
       </c>
       <c r="O56" t="n">
-        <v>100718.36</v>
+        <v>86633.35000000001</v>
       </c>
       <c r="P56" t="n">
-        <v>6834118.89</v>
+        <v>3759368.34</v>
       </c>
       <c r="Q56" t="n">
-        <v>-1848573.14</v>
+        <v>-1000477.06</v>
       </c>
       <c r="R56" t="n">
-        <v>-1962068.27</v>
+        <v>-1631871.13</v>
       </c>
       <c r="S56" t="n">
-        <v>-151077.54</v>
+        <v>-129950.02</v>
       </c>
       <c r="T56" t="n">
-        <v>-5736479.61</v>
+        <v>-5750977.96</v>
       </c>
       <c r="U56" t="inlineStr"/>
       <c r="V56" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W56" t="n">
-        <v>-42187191.44</v>
+        <v>-23308022.17</v>
       </c>
       <c r="X56" t="n">
-        <v>5035917.9</v>
+        <v>4331667.3</v>
       </c>
       <c r="Y56" t="n">
-        <v>1047470.92</v>
+        <v>1134896.83</v>
       </c>
       <c r="Z56" t="n">
-        <v>3988446.98</v>
+        <v>3196770.47</v>
       </c>
       <c r="AA56" t="n">
-        <v>3021550.74</v>
+        <v>2599000.38</v>
       </c>
       <c r="AB56" t="n">
-        <v>966896.24</v>
+        <v>597770.09</v>
       </c>
       <c r="AC56" t="n">
-        <v>52092809.3</v>
+        <v>31951798.52</v>
       </c>
       <c r="AD56" t="n">
-        <v>7849625.41</v>
+        <v>7512799.11</v>
       </c>
       <c r="AE56" t="n">
-        <v>44243183.89</v>
+        <v>24438999.41</v>
       </c>
     </row>
     <row r="57">
@@ -5833,86 +5823,86 @@
         <v>8</v>
       </c>
       <c r="D57" t="n">
-        <v>-4237528.68</v>
+        <v>-3776978.8</v>
       </c>
       <c r="E57" t="n">
-        <v>-498532.79</v>
+        <v>-444350.45</v>
       </c>
       <c r="F57" t="n">
-        <v>-249266.39</v>
+        <v>-222175.22</v>
       </c>
       <c r="G57" t="n">
-        <v>518474.1</v>
+        <v>582099.09</v>
       </c>
       <c r="H57" t="n">
-        <v>388855.57</v>
+        <v>436574.31</v>
       </c>
       <c r="I57" t="n">
-        <v>129618.52</v>
+        <v>145524.77</v>
       </c>
       <c r="J57" t="n">
-        <v>1246331.96</v>
+        <v>1110876.12</v>
       </c>
       <c r="K57" t="n">
-        <v>997065.5699999999</v>
+        <v>888700.89</v>
       </c>
       <c r="L57" t="n">
-        <v>747799.1800000001</v>
+        <v>666525.67</v>
       </c>
       <c r="M57" t="n">
-        <v>40342859.11</v>
+        <v>21710843.15</v>
       </c>
       <c r="N57" t="n">
-        <v>7304567.53</v>
+        <v>6557367.92</v>
       </c>
       <c r="O57" t="n">
-        <v>99706.56</v>
+        <v>88870.09</v>
       </c>
       <c r="P57" t="n">
-        <v>6846454.84</v>
+        <v>3766154.2</v>
       </c>
       <c r="Q57" t="n">
-        <v>-1885581.01</v>
+        <v>-1020506.3</v>
       </c>
       <c r="R57" t="n">
-        <v>-2146204.36</v>
+        <v>-1916940.8</v>
       </c>
       <c r="S57" t="n">
-        <v>-149559.84</v>
+        <v>-133305.13</v>
       </c>
       <c r="T57" t="n">
-        <v>-5211876.01</v>
+        <v>-4000280.1</v>
       </c>
       <c r="U57" t="inlineStr"/>
       <c r="V57" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W57" t="n">
-        <v>-43144374.39</v>
+        <v>-23921225.79</v>
       </c>
       <c r="X57" t="n">
-        <v>4985327.85</v>
+        <v>4443504.47</v>
       </c>
       <c r="Y57" t="n">
-        <v>1036948.19</v>
+        <v>1164198.17</v>
       </c>
       <c r="Z57" t="n">
-        <v>3948379.66</v>
+        <v>3279306.3</v>
       </c>
       <c r="AA57" t="n">
-        <v>2991196.71</v>
+        <v>2666102.68</v>
       </c>
       <c r="AB57" t="n">
-        <v>957182.95</v>
+        <v>613203.62</v>
       </c>
       <c r="AC57" t="n">
-        <v>52708007.03</v>
+        <v>31102729.06</v>
       </c>
       <c r="AD57" t="n">
-        <v>7507640.2</v>
+        <v>6050526.03</v>
       </c>
       <c r="AE57" t="n">
-        <v>45200366.83</v>
+        <v>25052203.03</v>
       </c>
     </row>
     <row r="58">
@@ -5928,86 +5918,86 @@
         <v>9</v>
       </c>
       <c r="D58" t="n">
-        <v>-4330872.16</v>
+        <v>-3870459.3</v>
       </c>
       <c r="E58" t="n">
-        <v>-509514.37</v>
+        <v>-455348.15</v>
       </c>
       <c r="F58" t="n">
-        <v>-254757.19</v>
+        <v>-227674.08</v>
       </c>
       <c r="G58" t="n">
-        <v>529894.95</v>
+        <v>596506.08</v>
       </c>
       <c r="H58" t="n">
-        <v>397421.21</v>
+        <v>447379.56</v>
       </c>
       <c r="I58" t="n">
-        <v>132473.74</v>
+        <v>149126.52</v>
       </c>
       <c r="J58" t="n">
-        <v>1273785.93</v>
+        <v>1138370.38</v>
       </c>
       <c r="K58" t="n">
-        <v>1019028.74</v>
+        <v>910696.3</v>
       </c>
       <c r="L58" t="n">
-        <v>764271.5600000001</v>
+        <v>683022.23</v>
       </c>
       <c r="M58" t="n">
-        <v>43054353.06</v>
+        <v>24015759.93</v>
       </c>
       <c r="N58" t="n">
-        <v>6983265.67</v>
+        <v>6765911.2</v>
       </c>
       <c r="O58" t="n">
-        <v>101902.87</v>
+        <v>91069.63</v>
       </c>
       <c r="P58" t="n">
-        <v>6858790.8</v>
+        <v>3772940.07</v>
       </c>
       <c r="Q58" t="n">
-        <v>-1922710.21</v>
+        <v>-1040601.21</v>
       </c>
       <c r="R58" t="n">
-        <v>-1844605.8</v>
+        <v>-2068303.23</v>
       </c>
       <c r="S58" t="n">
-        <v>-152854.31</v>
+        <v>-136604.45</v>
       </c>
       <c r="T58" t="n">
-        <v>-6899507.66</v>
+        <v>-5719588.46</v>
       </c>
       <c r="U58" t="inlineStr"/>
       <c r="V58" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W58" t="n">
-        <v>-44122641.98</v>
+        <v>-24549606.24</v>
       </c>
       <c r="X58" t="n">
-        <v>5095143.71</v>
+        <v>4553481.52</v>
       </c>
       <c r="Y58" t="n">
-        <v>1059789.89</v>
+        <v>1193012.16</v>
       </c>
       <c r="Z58" t="n">
-        <v>4035353.82</v>
+        <v>3360469.36</v>
       </c>
       <c r="AA58" t="n">
-        <v>3057086.23</v>
+        <v>2732088.91</v>
       </c>
       <c r="AB58" t="n">
-        <v>978267.59</v>
+        <v>628380.45</v>
       </c>
       <c r="AC58" t="n">
-        <v>55075602.2</v>
+        <v>33605079.61</v>
       </c>
       <c r="AD58" t="n">
-        <v>8896967.77</v>
+        <v>7924496.13</v>
       </c>
       <c r="AE58" t="n">
-        <v>46178634.43</v>
+        <v>25680583.48</v>
       </c>
     </row>
     <row r="59">
@@ -6023,86 +6013,86 @@
         <v>10</v>
       </c>
       <c r="D59" t="n">
-        <v>-4913237.11</v>
+        <v>-4808404.84</v>
       </c>
       <c r="E59" t="n">
-        <v>-578027.9</v>
+        <v>-565694.6899999999</v>
       </c>
       <c r="F59" t="n">
-        <v>-289013.95</v>
+        <v>-282847.34</v>
       </c>
       <c r="G59" t="n">
-        <v>601149.01</v>
+        <v>741060.04</v>
       </c>
       <c r="H59" t="n">
-        <v>450861.76</v>
+        <v>555795.03</v>
       </c>
       <c r="I59" t="n">
-        <v>150287.25</v>
+        <v>185265.01</v>
       </c>
       <c r="J59" t="n">
-        <v>1445069.74</v>
+        <v>1414236.72</v>
       </c>
       <c r="K59" t="n">
-        <v>1156055.79</v>
+        <v>1131389.38</v>
       </c>
       <c r="L59" t="n">
-        <v>867041.84</v>
+        <v>848542.03</v>
       </c>
       <c r="M59" t="n">
-        <v>41807639.08</v>
+        <v>24749614.74</v>
       </c>
       <c r="N59" t="n">
-        <v>9378052.59</v>
+        <v>9379994.539999999</v>
       </c>
       <c r="O59" t="n">
-        <v>115605.58</v>
+        <v>113138.94</v>
       </c>
       <c r="P59" t="n">
-        <v>6871126.75</v>
+        <v>3779725.93</v>
       </c>
       <c r="Q59" t="n">
-        <v>-1959960.75</v>
+        <v>-1060761.79</v>
       </c>
       <c r="R59" t="n">
-        <v>-2356520.03</v>
+        <v>-2544921.19</v>
       </c>
       <c r="S59" t="n">
-        <v>-173408.37</v>
+        <v>-169708.41</v>
       </c>
       <c r="T59" t="n">
-        <v>-6394086.87</v>
+        <v>-7785840.61</v>
       </c>
       <c r="U59" t="inlineStr"/>
       <c r="V59" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W59" t="n">
-        <v>-45232455.54</v>
+        <v>-25330264.91</v>
       </c>
       <c r="X59" t="n">
-        <v>5780278.96</v>
+        <v>5656946.88</v>
       </c>
       <c r="Y59" t="n">
-        <v>1202298.02</v>
+        <v>1482120.08</v>
       </c>
       <c r="Z59" t="n">
-        <v>4577980.93</v>
+        <v>4174826.79</v>
       </c>
       <c r="AA59" t="n">
-        <v>3468167.37</v>
+        <v>3394168.13</v>
       </c>
       <c r="AB59" t="n">
-        <v>1109813.56</v>
+        <v>780658.67</v>
       </c>
       <c r="AC59" t="n">
-        <v>56212463.25</v>
+        <v>36961712.36</v>
       </c>
       <c r="AD59" t="n">
-        <v>8924015.27</v>
+        <v>10500470.21</v>
       </c>
       <c r="AE59" t="n">
-        <v>47288447.99</v>
+        <v>26461242.15</v>
       </c>
     </row>
     <row r="60">
@@ -6118,86 +6108,86 @@
         <v>11</v>
       </c>
       <c r="D60" t="n">
-        <v>-5249125.58</v>
+        <v>-4525194.24</v>
       </c>
       <c r="E60" t="n">
-        <v>-617544.1899999999</v>
+        <v>-532375.79</v>
       </c>
       <c r="F60" t="n">
-        <v>-308772.09</v>
+        <v>-266187.9</v>
       </c>
       <c r="G60" t="n">
-        <v>642245.95</v>
+        <v>697412.29</v>
       </c>
       <c r="H60" t="n">
-        <v>481684.47</v>
+        <v>523059.22</v>
       </c>
       <c r="I60" t="n">
-        <v>160561.49</v>
+        <v>174353.07</v>
       </c>
       <c r="J60" t="n">
-        <v>1543860.47</v>
+        <v>1330939.48</v>
       </c>
       <c r="K60" t="n">
-        <v>1235088.37</v>
+        <v>1064751.59</v>
       </c>
       <c r="L60" t="n">
-        <v>926316.28</v>
+        <v>798563.6899999999</v>
       </c>
       <c r="M60" t="n">
-        <v>42314705.55</v>
+        <v>24757739.84</v>
       </c>
       <c r="N60" t="n">
-        <v>9150565.6</v>
+        <v>7118984.62</v>
       </c>
       <c r="O60" t="n">
-        <v>123508.84</v>
+        <v>106475.16</v>
       </c>
       <c r="P60" t="n">
-        <v>6883462.7</v>
+        <v>3786511.79</v>
       </c>
       <c r="Q60" t="n">
-        <v>-1997332.62</v>
+        <v>-1080988.04</v>
       </c>
       <c r="R60" t="n">
-        <v>-2532879.57</v>
+        <v>-2115014.39</v>
       </c>
       <c r="S60" t="n">
-        <v>-185263.26</v>
+        <v>-159712.74</v>
       </c>
       <c r="T60" t="n">
-        <v>-5282634.43</v>
+        <v>-5218075.49</v>
       </c>
       <c r="U60" t="inlineStr"/>
       <c r="V60" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W60" t="n">
-        <v>-46418140.38</v>
+        <v>-26064943.5</v>
       </c>
       <c r="X60" t="n">
-        <v>6175441.86</v>
+        <v>5323757.93</v>
       </c>
       <c r="Y60" t="n">
-        <v>1284491.91</v>
+        <v>1394824.58</v>
       </c>
       <c r="Z60" t="n">
-        <v>4890949.96</v>
+        <v>3928933.35</v>
       </c>
       <c r="AA60" t="n">
-        <v>3705265.12</v>
+        <v>3194254.76</v>
       </c>
       <c r="AB60" t="n">
-        <v>1185684.84</v>
+        <v>734678.59</v>
       </c>
       <c r="AC60" t="n">
-        <v>56474910.07</v>
+        <v>34688723.36</v>
       </c>
       <c r="AD60" t="n">
-        <v>8000777.25</v>
+        <v>7492802.62</v>
       </c>
       <c r="AE60" t="n">
-        <v>48474132.83</v>
+        <v>27195920.74</v>
       </c>
     </row>
     <row r="61">
@@ -6213,86 +6203,86 @@
         <v>12</v>
       </c>
       <c r="D61" t="n">
-        <v>-5356502.13</v>
+        <v>-4767680.01</v>
       </c>
       <c r="E61" t="n">
-        <v>-630176.72</v>
+        <v>-560903.53</v>
       </c>
       <c r="F61" t="n">
-        <v>-315088.36</v>
+        <v>-280451.77</v>
       </c>
       <c r="G61" t="n">
-        <v>655383.79</v>
+        <v>734783.62</v>
       </c>
       <c r="H61" t="n">
-        <v>491537.84</v>
+        <v>551087.72</v>
       </c>
       <c r="I61" t="n">
-        <v>163845.95</v>
+        <v>183695.91</v>
       </c>
       <c r="J61" t="n">
-        <v>1575441.8</v>
+        <v>1402258.83</v>
       </c>
       <c r="K61" t="n">
-        <v>1260353.44</v>
+        <v>1121807.06</v>
       </c>
       <c r="L61" t="n">
-        <v>945265.08</v>
+        <v>841355.3</v>
       </c>
       <c r="M61" t="n">
-        <v>44801221.68</v>
+        <v>24988416.19</v>
       </c>
       <c r="N61" t="n">
-        <v>9757656.48</v>
+        <v>8829223.939999999</v>
       </c>
       <c r="O61" t="n">
-        <v>126035.34</v>
+        <v>112180.71</v>
       </c>
       <c r="P61" t="n">
-        <v>6895798.66</v>
+        <v>3793297.66</v>
       </c>
       <c r="Q61" t="n">
-        <v>-2034825.83</v>
+        <v>-1101279.96</v>
       </c>
       <c r="R61" t="n">
-        <v>-2734211.06</v>
+        <v>-2223664.41</v>
       </c>
       <c r="S61" t="n">
-        <v>-189053.02</v>
+        <v>-168271.06</v>
       </c>
       <c r="T61" t="n">
-        <v>-6938550.12</v>
+        <v>-6259935.44</v>
       </c>
       <c r="U61" t="inlineStr"/>
       <c r="V61" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W61" t="n">
-        <v>-47628079.69</v>
+        <v>-26838990.38</v>
       </c>
       <c r="X61" t="n">
-        <v>6301767.22</v>
+        <v>5609035.3</v>
       </c>
       <c r="Y61" t="n">
-        <v>1310767.58</v>
+        <v>1469567.25</v>
       </c>
       <c r="Z61" t="n">
-        <v>4990999.64</v>
+        <v>4139468.05</v>
       </c>
       <c r="AA61" t="n">
-        <v>3781060.33</v>
+        <v>3365421.18</v>
       </c>
       <c r="AB61" t="n">
-        <v>1209939.31</v>
+        <v>774046.87</v>
       </c>
       <c r="AC61" t="n">
-        <v>59545886.33</v>
+        <v>36621838.52</v>
       </c>
       <c r="AD61" t="n">
-        <v>9861814.199999999</v>
+        <v>8651870.91</v>
       </c>
       <c r="AE61" t="n">
-        <v>49684072.13</v>
+        <v>27969967.61</v>
       </c>
     </row>
     <row r="62">
@@ -6308,86 +6298,181 @@
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>-3989332.29</v>
+        <v>-3621946.75</v>
       </c>
       <c r="E62" t="n">
-        <v>-469333.21</v>
+        <v>-426111.38</v>
       </c>
       <c r="F62" t="n">
-        <v>-234666.61</v>
+        <v>-213055.69</v>
       </c>
       <c r="G62" t="n">
-        <v>488106.54</v>
+        <v>558205.91</v>
       </c>
       <c r="H62" t="n">
-        <v>366079.9</v>
+        <v>418654.43</v>
       </c>
       <c r="I62" t="n">
-        <v>122026.63</v>
+        <v>139551.48</v>
       </c>
       <c r="J62" t="n">
-        <v>1173333.03</v>
+        <v>1065278.46</v>
       </c>
       <c r="K62" t="n">
-        <v>938666.42</v>
+        <v>852222.76</v>
       </c>
       <c r="L62" t="n">
-        <v>703999.8199999999</v>
+        <v>639167.0699999999</v>
       </c>
       <c r="M62" t="n">
-        <v>45962230.7</v>
+        <v>27633593.98</v>
       </c>
       <c r="N62" t="n">
-        <v>7319927.28</v>
+        <v>6022580.94</v>
       </c>
       <c r="O62" t="n">
-        <v>93866.64</v>
+        <v>85222.28</v>
       </c>
       <c r="P62" t="n">
-        <v>6908134.61</v>
+        <v>3800083.52</v>
       </c>
       <c r="Q62" t="n">
-        <v>-2072440.38</v>
+        <v>-1121637.55</v>
       </c>
       <c r="R62" t="n">
-        <v>-2044253.93</v>
+        <v>-1728475.88</v>
       </c>
       <c r="S62" t="n">
-        <v>-140799.96</v>
+        <v>-127833.41</v>
       </c>
       <c r="T62" t="n">
-        <v>-5441473.07</v>
+        <v>-6005532.55</v>
       </c>
       <c r="U62" t="inlineStr"/>
       <c r="V62" t="n">
-        <v>-2055992.44</v>
+        <v>-1130977.24</v>
       </c>
       <c r="W62" t="n">
-        <v>-48529199.45</v>
+        <v>-27427024.08</v>
       </c>
       <c r="X62" t="n">
-        <v>4693332.11</v>
+        <v>4261113.82</v>
       </c>
       <c r="Y62" t="n">
-        <v>976213.08</v>
+        <v>1116411.82</v>
       </c>
       <c r="Z62" t="n">
-        <v>3717119.03</v>
+        <v>3144702</v>
       </c>
       <c r="AA62" t="n">
-        <v>2815999.27</v>
+        <v>2556668.29</v>
       </c>
       <c r="AB62" t="n">
-        <v>901119.76</v>
+        <v>588033.71</v>
       </c>
       <c r="AC62" t="n">
-        <v>58211718.86</v>
+        <v>36419843.16</v>
       </c>
       <c r="AD62" t="n">
-        <v>7626526.96</v>
+        <v>7861841.84</v>
       </c>
       <c r="AE62" t="n">
-        <v>50585191.9</v>
+        <v>28558001.32</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C63" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" t="n">
+        <v>-3624897.51</v>
+      </c>
+      <c r="E63" t="n">
+        <v>-426458.53</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-213229.27</v>
+      </c>
+      <c r="G63" t="n">
+        <v>558660.6800000001</v>
+      </c>
+      <c r="H63" t="n">
+        <v>418995.51</v>
+      </c>
+      <c r="I63" t="n">
+        <v>139665.17</v>
+      </c>
+      <c r="J63" t="n">
+        <v>1066146.33</v>
+      </c>
+      <c r="K63" t="n">
+        <v>852917.0600000001</v>
+      </c>
+      <c r="L63" t="n">
+        <v>639687.8</v>
+      </c>
+      <c r="M63" t="n">
+        <v>27576137.3</v>
+      </c>
+      <c r="N63" t="n">
+        <v>5693644.51</v>
+      </c>
+      <c r="O63" t="n">
+        <v>85291.71000000001</v>
+      </c>
+      <c r="P63" t="n">
+        <v>3806869.38</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>-1142060.81</v>
+      </c>
+      <c r="R63" t="n">
+        <v>-1986978.94</v>
+      </c>
+      <c r="S63" t="n">
+        <v>-127937.56</v>
+      </c>
+      <c r="T63" t="n">
+        <v>-4758451.49</v>
+      </c>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="n">
+        <v>-1130977.24</v>
+      </c>
+      <c r="W63" t="n">
+        <v>-28015536.86</v>
+      </c>
+      <c r="X63" t="n">
+        <v>4264585.31</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>1117321.35</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>3147263.96</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>2558751.19</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>588512.77</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>36019882.08</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>6873367.99</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>29146514.09</v>
       </c>
     </row>
   </sheetData>
